--- a/internal_doc/05.测试设计/参数校验/元数据参数校验测试设计.xlsx
+++ b/internal_doc/05.测试设计/参数校验/元数据参数校验测试设计.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="101">
   <si>
     <t>Domain</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -131,18 +131,6 @@
   </si>
   <si>
     <t>是</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>不能删除不为空的域；
-不能删除系统域；
-不能删除不存在的域；</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、全局唯一
-2、字符有效，即不为空串且不包含点（.）或$，如testDomain
-3、有效长度：1B、127B</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -1022,75 +1010,11 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">createDomain
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>语法：</t>
-    </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">createDomain
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>语法：</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>b.createCS(&lt; name &gt;,[ options ])</t>
-    </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">createDomain
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>语法：</t>
-    </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>options:PageSize</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>options:Domain</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>options:LobPageSize</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -1133,12 +1057,895 @@
     </r>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
+  <si>
+    <r>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">、不存在的域
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">系统域
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、空串</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、已存在的域，非系统域
+2、不指定域</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1、有效取值：0，4096，8192，16384，32768，65536
+2、db.createCS(&lt; name &gt;,[ PageSize ])方式创建CS，如：db.createCS("testCS",</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>[4096,8192]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>)
+3、不指定PageSize，即默认为65536</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>options:LobPageSize</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、有效取值：0，4096，8192，16384，32768，65536，131072，262144，524288
+2、不指定LobPageSize</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">dropCS
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>语法：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>db.dropCS(&lt; name &gt;)</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>CS必须存在</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>不能删除不为空的域；
+不能删除系统域；
+域必须存在。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、已存在的CS
+2、为空的CS
+3、非空的CS</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">getCS
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>语法：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>db.getCS(&lt; name &gt;)</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1、已存在的CS，非系统CS
+2、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>系统CS（直连编目）</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、不存在的</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>CS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>系统</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>CS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、空串，如</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>db.dropCS(“”)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、不指定</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>CS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>，如</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>db.dropCS()</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、不存在的</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>CS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+2、空串，如db.getCS(“”)
+4、不指定CS，如db.getCS()</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">listCollectionSpaces
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>语法：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>db.listCollectionSpaces()</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、加条件查询，如：db.listCollectionSpaces(“test”)
+2、空串，如：db.listCollectionSpaces(‘’)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>CL</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">createCL
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>语法：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>db.collectionspace.createCL(&lt; name &gt;,[ options ])</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">createCS
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>语法：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>db.createCS(&lt; name &gt;,[ options ])</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>options:ShardingKey</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>options:ShardingType</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>options:Partition</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>options:ReplSize</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>options:Compressed</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>options:IsMainCL</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>options:AutoSplit</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>options:Group</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>options:AutoIndexId</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>默认为hash分区
+ShardingType:"hash"|"range"</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">
+</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">hash 分区时填写，代表了 hash 分区的个数。其值必须是2的幂。范围在[2^3, 2^20]
+</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Compressed:true|false</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、无效取值：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>65537</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>4096.5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>-1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、空串</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、无效取值：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>524287</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>4096.5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>-1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、空串</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、全局唯一
+2、字符有效，即不为空串且不包含点（.）或$，如test
+3、有效长度：1B、127B</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、全局唯一
+2、字符有效，即不为空串且不包含点（.）或$，如test
+3、有效长度：1B、127B</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">IsMainCL:true|false
+</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">AutoSplit:true|false
+</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">AutoIndexId:true|false
+</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">格式：ShardingKey:{&lt; 字段1 &gt; : &lt; 1|-1 &gt;,[&lt; 字段2 &gt;:&lt; 1|-1 &gt;, ...]}
+</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">ReplSize: &lt; int num &gt;
+默认情况下，副本写入个数为1
+</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">dropCL
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>语法：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>db.dropCS(&lt; name &gt;)</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">getCL
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>语法：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>db.getCS(&lt; name &gt;)</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">listCollections
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>语法：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>db.collectionSpaces.listCollections()</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1198,6 +2005,12 @@
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color rgb="FFFF0000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -1304,7 +2117,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -1317,30 +2130,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -1372,10 +2161,28 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1386,6 +2193,15 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1681,358 +2497,646 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H32"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="12.25" style="4" customWidth="1"/>
-    <col min="2" max="2" width="24.375" style="15" customWidth="1"/>
-    <col min="3" max="3" width="15.625" style="15" customWidth="1"/>
-    <col min="4" max="4" width="27.75" style="15" customWidth="1"/>
-    <col min="5" max="5" width="10.625" style="21" customWidth="1"/>
-    <col min="6" max="6" width="26.125" style="15" customWidth="1"/>
-    <col min="7" max="7" width="31.875" style="15" customWidth="1"/>
-    <col min="8" max="8" width="9" style="15"/>
+    <col min="2" max="2" width="24.375" style="7" customWidth="1"/>
+    <col min="3" max="3" width="15.625" style="7" customWidth="1"/>
+    <col min="4" max="4" width="27.75" style="7" customWidth="1"/>
+    <col min="5" max="5" width="10.625" style="13" customWidth="1"/>
+    <col min="6" max="6" width="26.125" style="7" customWidth="1"/>
+    <col min="7" max="7" width="31.875" style="7" customWidth="1"/>
+    <col min="8" max="8" width="9" style="7"/>
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="17" customFormat="1">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:8" s="9" customFormat="1">
+      <c r="A1" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="D1" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="12"/>
-      <c r="F1" s="5" t="s">
+      <c r="E1" s="19"/>
+      <c r="F1" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="16" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:8" s="17" customFormat="1">
-      <c r="A2" s="6"/>
-      <c r="B2" s="6"/>
-      <c r="C2" s="6"/>
+    <row r="2" spans="1:8" s="9" customFormat="1">
+      <c r="A2" s="17"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
       <c r="D2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="18" t="s">
+      <c r="E2" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
+      <c r="H2" s="17"/>
     </row>
     <row r="3" spans="1:8" ht="67.5">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="C3" s="13" t="s">
+      <c r="B3" s="22" t="s">
+        <v>38</v>
+      </c>
+      <c r="C3" s="5" t="s">
         <v>1</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="19" t="s">
+      <c r="E3" s="11" t="s">
         <v>9</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="G3" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="H3" s="16"/>
+        <v>92</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="H3" s="8"/>
     </row>
     <row r="4" spans="1:8" ht="40.5">
-      <c r="A4" s="8"/>
-      <c r="B4" s="14"/>
-      <c r="C4" s="13" t="s">
+      <c r="A4" s="21"/>
+      <c r="B4" s="22"/>
+      <c r="C4" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="13" t="s">
+      <c r="D4" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E4" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G4" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="E4" s="19" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G4" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="H4" s="16"/>
+      <c r="H4" s="8"/>
     </row>
     <row r="5" spans="1:8" ht="38.25">
-      <c r="A5" s="8"/>
-      <c r="B5" s="14"/>
-      <c r="C5" s="13" t="s">
+      <c r="A5" s="21"/>
+      <c r="B5" s="22"/>
+      <c r="C5" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="13" t="s">
+      <c r="D5" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="E5" s="19" t="s">
+      <c r="E5" s="11" t="s">
         <v>10</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="G5" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="H5" s="16"/>
+        <v>24</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="H5" s="8"/>
     </row>
     <row r="6" spans="1:8" ht="67.5">
-      <c r="A6" s="8"/>
-      <c r="B6" s="13" t="s">
+      <c r="A6" s="21"/>
+      <c r="B6" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="13" t="s">
+      <c r="C6" s="5" t="s">
         <v>18</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E6" s="19" t="s">
+        <v>65</v>
+      </c>
+      <c r="E6" s="11" t="s">
         <v>19</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="G6" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="H6" s="16"/>
+      <c r="G6" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="H6" s="8"/>
     </row>
     <row r="7" spans="1:8" ht="51.75">
-      <c r="A7" s="8"/>
-      <c r="B7" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="C7" s="13" t="s">
+      <c r="A7" s="21"/>
+      <c r="B7" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" s="5" t="s">
         <v>18</v>
       </c>
       <c r="D7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E7" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G7" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="E7" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="G7" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="H7" s="16"/>
+      <c r="H7" s="8"/>
     </row>
     <row r="8" spans="1:8" ht="38.25">
-      <c r="A8" s="8"/>
-      <c r="B8" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="C8" s="24" t="s">
+      <c r="A8" s="21"/>
+      <c r="B8" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C8" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="D8" s="15"/>
+      <c r="E8" s="11"/>
+      <c r="F8" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="D8" s="24"/>
-      <c r="E8" s="19"/>
-      <c r="F8" s="2" t="s">
-        <v>36</v>
-      </c>
       <c r="G8" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="H8" s="16"/>
+        <v>46</v>
+      </c>
+      <c r="H8" s="8"/>
     </row>
     <row r="9" spans="1:8" ht="45.75" customHeight="1">
-      <c r="A9" s="8"/>
-      <c r="B9" s="14" t="s">
+      <c r="A9" s="21"/>
+      <c r="B9" s="22" t="s">
+        <v>41</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C9" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="E9" s="25" t="s">
+      <c r="E9" s="23" t="s">
+        <v>37</v>
+      </c>
+      <c r="F9" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="F9" s="2" t="s">
-        <v>41</v>
-      </c>
       <c r="G9" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="H9" s="16"/>
+        <v>42</v>
+      </c>
+      <c r="H9" s="8"/>
     </row>
     <row r="10" spans="1:8" ht="67.5">
-      <c r="A10" s="8"/>
-      <c r="B10" s="14"/>
-      <c r="C10" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="D10" s="13" t="s">
+      <c r="A10" s="21"/>
+      <c r="B10" s="22"/>
+      <c r="C10" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D10" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="E10" s="26"/>
+      <c r="E10" s="24"/>
       <c r="F10" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="G10" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="H10" s="16"/>
+        <v>40</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="H10" s="8"/>
     </row>
     <row r="11" spans="1:8" ht="51">
-      <c r="A11" s="8"/>
-      <c r="B11" s="13" t="s">
+      <c r="A11" s="21"/>
+      <c r="B11" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="C11" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="D11" s="14"/>
+      <c r="E11" s="12"/>
+      <c r="F11" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="G11" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="C11" s="24" t="s">
-        <v>34</v>
-      </c>
-      <c r="D11" s="22"/>
-      <c r="E11" s="20"/>
-      <c r="F11" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="H11" s="16"/>
+      <c r="H11" s="8"/>
     </row>
     <row r="12" spans="1:8" ht="51">
-      <c r="A12" s="8"/>
+      <c r="A12" s="21"/>
       <c r="B12" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="C12" s="24" t="s">
+        <v>48</v>
+      </c>
+      <c r="C12" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="D12" s="14"/>
+      <c r="E12" s="12"/>
+      <c r="F12" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="D12" s="22"/>
-      <c r="E12" s="20"/>
-      <c r="F12" s="2" t="s">
-        <v>36</v>
-      </c>
       <c r="G12" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="H12" s="16"/>
+        <v>49</v>
+      </c>
+      <c r="H12" s="8"/>
     </row>
     <row r="13" spans="1:8" ht="64.5">
-      <c r="A13" s="27" t="s">
-        <v>52</v>
-      </c>
-      <c r="B13" s="9" t="s">
-        <v>54</v>
+      <c r="A13" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="B13" s="26" t="s">
+        <v>75</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>18</v>
       </c>
       <c r="D13" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E13" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="H13" s="8"/>
+    </row>
+    <row r="14" spans="1:8" ht="102">
+      <c r="A14" s="25"/>
+      <c r="B14" s="27"/>
+      <c r="C14" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E14" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="F14" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="E13" s="19" t="s">
+      <c r="G14" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="H14" s="8"/>
+    </row>
+    <row r="15" spans="1:8" ht="40.5">
+      <c r="A15" s="25"/>
+      <c r="B15" s="27"/>
+      <c r="C15" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E15" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="G15" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="H15" s="8"/>
+    </row>
+    <row r="16" spans="1:8" ht="51">
+      <c r="A16" s="25"/>
+      <c r="B16" s="28"/>
+      <c r="C16" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E16" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="G16" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="H16" s="8"/>
+    </row>
+    <row r="17" spans="1:8" ht="54">
+      <c r="A17" s="25"/>
+      <c r="B17" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E17" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="F13" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="G13" s="13" t="s">
-        <v>63</v>
-      </c>
-      <c r="H13" s="16"/>
+      <c r="F17" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G17" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="H17" s="8"/>
     </row>
-    <row r="14" spans="1:8" ht="89.25">
-      <c r="A14" s="27"/>
-      <c r="B14" s="10"/>
-      <c r="C14" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="E14" s="19" t="s">
+    <row r="18" spans="1:8" ht="39">
+      <c r="A18" s="25"/>
+      <c r="B18" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E18" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G18" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="H18" s="8"/>
+    </row>
+    <row r="19" spans="1:8" ht="51">
+      <c r="A19" s="25"/>
+      <c r="B19" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="C19" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="D19" s="15"/>
+      <c r="E19" s="11"/>
+      <c r="F19" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="H19" s="8"/>
+    </row>
+    <row r="20" spans="1:8" ht="64.5">
+      <c r="A20" s="25" t="s">
+        <v>73</v>
+      </c>
+      <c r="B20" s="26" t="s">
+        <v>74</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E20" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="G20" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="H20" s="8"/>
+    </row>
+    <row r="21" spans="1:8" ht="51">
+      <c r="A21" s="25"/>
+      <c r="B21" s="27"/>
+      <c r="C21" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E21" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="F14" s="2"/>
-      <c r="G14" s="13"/>
-      <c r="H14" s="16"/>
+      <c r="F21" s="2"/>
+      <c r="G21" s="6"/>
+      <c r="H21" s="8"/>
     </row>
-    <row r="15" spans="1:8" ht="38.25">
-      <c r="A15" s="27"/>
-      <c r="B15" s="10"/>
-      <c r="C15" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="E15" s="19" t="s">
+    <row r="22" spans="1:8" ht="25.5">
+      <c r="A22" s="25"/>
+      <c r="B22" s="27"/>
+      <c r="C22" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E22" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="F15" s="2"/>
-      <c r="G15" s="13"/>
-      <c r="H15" s="16"/>
+      <c r="F22" s="2"/>
+      <c r="G22" s="6"/>
+      <c r="H22" s="8"/>
     </row>
-    <row r="16" spans="1:8" ht="38.25">
-      <c r="A16" s="27"/>
-      <c r="B16" s="23"/>
-      <c r="C16" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="E16" s="19" t="s">
+    <row r="23" spans="1:8" ht="51">
+      <c r="A23" s="25"/>
+      <c r="B23" s="27"/>
+      <c r="C23" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="E23" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="F16" s="2"/>
-      <c r="G16" s="13"/>
-      <c r="H16" s="16"/>
+      <c r="F23" s="2"/>
+      <c r="G23" s="6"/>
+      <c r="H23" s="8"/>
     </row>
-    <row r="17" spans="1:8" ht="26.25">
-      <c r="A17" s="27"/>
-      <c r="B17" s="13" t="s">
-        <v>53</v>
-      </c>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
-      <c r="E17" s="19"/>
-      <c r="F17" s="2"/>
-      <c r="G17" s="13"/>
-      <c r="H17" s="16"/>
+    <row r="24" spans="1:8" ht="38.25">
+      <c r="A24" s="25"/>
+      <c r="B24" s="27"/>
+      <c r="C24" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="E24" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="F24" s="2"/>
+      <c r="G24" s="6"/>
+      <c r="H24" s="8"/>
     </row>
-    <row r="18" spans="1:8" ht="26.25">
-      <c r="A18" s="27"/>
-      <c r="B18" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
-      <c r="E18" s="19"/>
-      <c r="F18" s="2"/>
-      <c r="G18" s="13"/>
-      <c r="H18" s="16"/>
+    <row r="25" spans="1:8" ht="25.5">
+      <c r="A25" s="25"/>
+      <c r="B25" s="27"/>
+      <c r="C25" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E25" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="F25" s="2"/>
+      <c r="G25" s="6"/>
+      <c r="H25" s="8"/>
+    </row>
+    <row r="26" spans="1:8" ht="25.5">
+      <c r="A26" s="25"/>
+      <c r="B26" s="27"/>
+      <c r="C26" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E26" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="F26" s="2"/>
+      <c r="G26" s="6"/>
+      <c r="H26" s="8"/>
+    </row>
+    <row r="27" spans="1:8" ht="25.5">
+      <c r="A27" s="25"/>
+      <c r="B27" s="27"/>
+      <c r="C27" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="E27" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="F27" s="2"/>
+      <c r="G27" s="6"/>
+      <c r="H27" s="8"/>
+    </row>
+    <row r="28" spans="1:8" ht="25.5">
+      <c r="A28" s="25"/>
+      <c r="B28" s="27"/>
+      <c r="C28" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="E28" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="F28" s="2"/>
+      <c r="G28" s="6"/>
+      <c r="H28" s="8"/>
+    </row>
+    <row r="29" spans="1:8" ht="25.5">
+      <c r="A29" s="25"/>
+      <c r="B29" s="28"/>
+      <c r="C29" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="E29" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="F29" s="2"/>
+      <c r="G29" s="6"/>
+      <c r="H29" s="8"/>
+    </row>
+    <row r="30" spans="1:8" ht="54">
+      <c r="A30" s="25"/>
+      <c r="B30" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E30" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G30" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="H30" s="8"/>
+    </row>
+    <row r="31" spans="1:8" ht="39">
+      <c r="A31" s="25"/>
+      <c r="B31" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E31" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G31" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="H31" s="8"/>
+    </row>
+    <row r="32" spans="1:8" ht="53.25">
+      <c r="A32" s="25"/>
+      <c r="B32" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="C32" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="D32" s="15"/>
+      <c r="E32" s="11"/>
+      <c r="F32" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="H32" s="8"/>
     </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="15">
+    <mergeCell ref="B13:B16"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="A13:A19"/>
+    <mergeCell ref="A20:A32"/>
+    <mergeCell ref="B20:B29"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
     <mergeCell ref="D1:E1"/>
@@ -2040,12 +3144,6 @@
     <mergeCell ref="B9:B10"/>
     <mergeCell ref="E9:E10"/>
     <mergeCell ref="B3:B5"/>
-    <mergeCell ref="A13:A18"/>
-    <mergeCell ref="B13:B16"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="A1:A2"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/internal_doc/05.测试设计/参数校验/元数据参数校验测试设计.xlsx
+++ b/internal_doc/05.测试设计/参数校验/元数据参数校验测试设计.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="125">
   <si>
     <t>Domain</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -30,14 +30,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>options:Autosplit</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>子特性</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>参数项</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -71,10 +63,6 @@
   </si>
   <si>
     <t>备注</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>特性</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -395,12 +383,6 @@
       </rPr>
       <t>、不指定组</t>
     </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、true
-2、false
-3、不指定AutoSplit</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -724,11 +706,6 @@
   </si>
   <si>
     <t>1、存在的组</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、true
-2、false</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -1202,12 +1179,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>1、已存在的CS
-2、为空的CS
-3、非空的CS</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <t xml:space="preserve">getCS
 </t>
@@ -1582,25 +1553,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>默认为hash分区
-ShardingType:"hash"|"range"</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">
-</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">hash 分区时填写，代表了 hash 分区的个数。其值必须是2的幂。范围在[2^3, 2^20]
-</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Compressed:true|false</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <t>1</t>
     </r>
@@ -1842,24 +1794,795 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">AutoSplit:true|false
+    <r>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、名称重复
+2、字符无效：包含（.）包含$
+3、无效长度：空串、128B
+4、不指定name
+5、格式错误，如：不带引号输入</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、字段值无效，如</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>ShardingKey:{"age":0}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+2、空串，如ShardingKey:{"age":} 或 ShardingKey:{}</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、单分区键，取值1|-1
+2、多分区键，取值1|-1
+3、不指定ShardingKey</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">格式：ShardingKey:{&lt; 字段1 &gt; : &lt; 1|-1 &gt;,[&lt; 字段2 &gt;:&lt; 1|-1 &gt;, ...]}
+需要分区，必须指定 ShardingKey
 </t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">AutoIndexId:true|false
+    <r>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、字段值无效，如</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>ShardingType:"test"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+2、空串，如ShardingType:"" 或 ShardingType:{}</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">hash 分区时填写，代表了 hash 分区的个数。其值必须是2的幂。范围在[2^3, 2^20]，即为8~1048576范围内2的幂次方取值
 </t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">格式：ShardingKey:{&lt; 字段1 &gt; : &lt; 1|-1 &gt;,[&lt; 字段2 &gt;:&lt; 1|-1 &gt;, ...]}
+    <r>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>hash</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>分区，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Partition</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>无效取值：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>4(2^2)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>2097152</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>2^21</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>）、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>7</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>1048577
+2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>range</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>分区，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Partition</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>取有效值，如</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>1024
+3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、空值，如</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Partition</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>：</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ReplSize: &lt; int num &gt;
+默认情况下，副本写入个数为1；取值为0，则副本数等于数据组节点个数；手动指定副本写入个数时，不能超出当前组内节点个数。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1、hash分区，Partition有效取值：8、1048576
+2、不指定Partition，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>默认为？</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、不指定shardingType
+2、ShardingType:"hash"
+3、ShardingType:"range"</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>ReplSize</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>无效取值：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>-1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、空</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+     ReplSize</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>取值大于当前组内节点个数</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、不指定ReplSize，默认为1
+2、ReplSize:0
+   ReplSize取值等于数据组节点个数</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Compressed:true|false</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、取值非法，如</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>test
+2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、空串</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>AutoSplit:true|false
+AutoSplit 必须配合散列分区和域使用，且不能与 Group 同时使用。
+如果在集合中没有指定AutoSplit，则使用所属域中的AutoSplit参数。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>options:Autosplit</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Autosplit:true|false</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、Autosplit:true
+   Autosplit:false
+2、不指定AutoSplit</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Group必须存在于集合空间所属的域中（所有复制组均属于SYSDOMAIN，即如果集合空间没有指定域，则系统内任意复制组均可）。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>默认为hash分区
+ShardingType:"hash"|"range"</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1、不指定Compressed，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>默认为false</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+2、Compressed:true|false</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1、不指定IsMainCL，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>默认为false</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+2、IsMainCL:true|false</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、ShardingType:"hash"，AutoSplit:true，且不指定Group
+2、AutoSplit:false
+3、域中AutoSplit:true，CL不指定AutoSplit</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、取值非法，如</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>test
+2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、空串</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>ShardingType:"range"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>AutoSplit:true
+2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>AutoSplit:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>和</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Group</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>一起使用，如：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>AutoSplit:false,Group:group1
+3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、取值非法，如</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>test
+4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、空串</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、所属CS指定域，指定CL的Group为CS所属域中的group
+2、所属CS不指定域，指定CL的Group为系统内任意复制组</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">1、所属CS指定域，指定CL的Group为CS所属域中的group
+2、空串
 </t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">ReplSize: &lt; int num &gt;
-默认情况下，副本写入个数为1
-</t>
+    <t>AutoIndexId:true|false</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1、不指定Compressed，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>默认为？</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+2、Compressed:true|false</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>CL必须存在</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>已存在的CS</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -1884,7 +2607,7 @@
         <rFont val="Times New Roman"/>
         <family val="1"/>
       </rPr>
-      <t>db.dropCS(&lt; name &gt;)</t>
+      <t>db.collectionspace.dropCL(&lt; name &gt;)</t>
     </r>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -1910,7 +2633,247 @@
         <rFont val="Times New Roman"/>
         <family val="1"/>
       </rPr>
-      <t>db.getCS(&lt; name &gt;)</t>
+      <t>db.collectionspace.getCL(&lt; name &gt;)</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>已存在的CL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>，非系统CS</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、不存在的</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>CL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>系统</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>CL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、空串，如</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>db.collectionspace.dropCL(“”)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、不指定</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>CL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>，如</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>db.collectionspace.dropCL()</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>已存在的CL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t/>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、不存在的</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>CL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+2、空串，如db.collectionspace.getCL(“”)
+4、不指定CL，如db.collectionspace.getCL()</t>
     </r>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -1936,8 +2899,21 @@
         <rFont val="Times New Roman"/>
         <family val="1"/>
       </rPr>
-      <t>db.collectionSpaces.listCollections()</t>
-    </r>
+      <t>db.listCollections()</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、加条件查询，如：db.listCollections(“test”)
+2、空串，如：db.listCollections(‘’)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>子特性</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>特性</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -2117,7 +3093,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -2164,10 +3140,25 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2190,18 +3181,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2512,629 +3491,659 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" s="9" customFormat="1">
-      <c r="A1" s="16" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="16" t="s">
+      <c r="A1" s="20" t="s">
+        <v>124</v>
+      </c>
+      <c r="B1" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="C1" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="18" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="19"/>
-      <c r="F1" s="16" t="s">
+      <c r="E1" s="24"/>
+      <c r="F1" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1" s="20" t="s">
         <v>11</v>
-      </c>
-      <c r="G1" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="H1" s="16" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:8" s="9" customFormat="1">
-      <c r="A2" s="17"/>
-      <c r="B2" s="17"/>
-      <c r="C2" s="17"/>
+      <c r="A2" s="21"/>
+      <c r="B2" s="21"/>
+      <c r="C2" s="21"/>
       <c r="D2" s="3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="F2" s="17"/>
-      <c r="G2" s="17"/>
-      <c r="H2" s="17"/>
+        <v>5</v>
+      </c>
+      <c r="F2" s="21"/>
+      <c r="G2" s="21"/>
+      <c r="H2" s="21"/>
     </row>
     <row r="3" spans="1:8" ht="67.5">
-      <c r="A3" s="20" t="s">
+      <c r="A3" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="22" t="s">
-        <v>38</v>
+      <c r="B3" s="27" t="s">
+        <v>34</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>1</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E3" s="11" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="H3" s="8"/>
     </row>
     <row r="4" spans="1:8" ht="40.5">
-      <c r="A4" s="21"/>
-      <c r="B4" s="22"/>
+      <c r="A4" s="26"/>
+      <c r="B4" s="27"/>
       <c r="C4" s="5" t="s">
         <v>2</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="H4" s="8"/>
     </row>
     <row r="5" spans="1:8" ht="38.25">
-      <c r="A5" s="21"/>
-      <c r="B5" s="22"/>
-      <c r="C5" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>16</v>
+      <c r="A5" s="26"/>
+      <c r="B5" s="27"/>
+      <c r="C5" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="D5" s="16" t="s">
+        <v>100</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>24</v>
+        <v>101</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H5" s="8"/>
     </row>
     <row r="6" spans="1:8" ht="67.5">
-      <c r="A6" s="21"/>
+      <c r="A6" s="26"/>
       <c r="B6" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="H6" s="8"/>
     </row>
     <row r="7" spans="1:8" ht="51.75">
-      <c r="A7" s="21"/>
+      <c r="A7" s="26"/>
       <c r="B7" s="5" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="H7" s="8"/>
     </row>
     <row r="8" spans="1:8" ht="38.25">
-      <c r="A8" s="21"/>
+      <c r="A8" s="26"/>
       <c r="B8" s="5" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="D8" s="15"/>
       <c r="E8" s="11"/>
       <c r="F8" s="2" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="H8" s="8"/>
     </row>
     <row r="9" spans="1:8" ht="45.75" customHeight="1">
-      <c r="A9" s="21"/>
-      <c r="B9" s="22" t="s">
-        <v>41</v>
+      <c r="A9" s="26"/>
+      <c r="B9" s="27" t="s">
+        <v>36</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="E9" s="23" t="s">
+        <v>38</v>
+      </c>
+      <c r="E9" s="28" t="s">
+        <v>33</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G9" s="2" t="s">
         <v>37</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>42</v>
       </c>
       <c r="H9" s="8"/>
     </row>
     <row r="10" spans="1:8" ht="67.5">
-      <c r="A10" s="21"/>
-      <c r="B10" s="22"/>
+      <c r="A10" s="26"/>
+      <c r="B10" s="27"/>
       <c r="C10" s="5" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="E10" s="24"/>
+        <v>13</v>
+      </c>
+      <c r="E10" s="29"/>
       <c r="F10" s="2" t="s">
-        <v>40</v>
+        <v>101</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="H10" s="8"/>
     </row>
     <row r="11" spans="1:8" ht="51">
-      <c r="A11" s="21"/>
+      <c r="A11" s="26"/>
       <c r="B11" s="5" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="C11" s="15" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="D11" s="14"/>
       <c r="E11" s="12"/>
       <c r="F11" s="2" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="H11" s="8"/>
     </row>
     <row r="12" spans="1:8" ht="51">
-      <c r="A12" s="21"/>
+      <c r="A12" s="26"/>
       <c r="B12" s="1" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="D12" s="14"/>
       <c r="E12" s="12"/>
       <c r="F12" s="2" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="H12" s="8"/>
     </row>
     <row r="13" spans="1:8" ht="64.5">
-      <c r="A13" s="25" t="s">
-        <v>50</v>
-      </c>
-      <c r="B13" s="26" t="s">
-        <v>75</v>
+      <c r="A13" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="B13" s="17" t="s">
+        <v>69</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="H13" s="8"/>
     </row>
     <row r="14" spans="1:8" ht="102">
-      <c r="A14" s="25"/>
-      <c r="B14" s="27"/>
+      <c r="A14" s="22"/>
+      <c r="B14" s="18"/>
       <c r="C14" s="2" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="D14" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E14" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="E14" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>60</v>
-      </c>
       <c r="G14" s="6" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H14" s="8"/>
     </row>
     <row r="15" spans="1:8" ht="40.5">
-      <c r="A15" s="25"/>
-      <c r="B15" s="27"/>
+      <c r="A15" s="22"/>
+      <c r="B15" s="18"/>
       <c r="C15" s="2" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="D15" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E15" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="G15" s="6" t="s">
         <v>53</v>
-      </c>
-      <c r="E15" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="G15" s="6" t="s">
-        <v>58</v>
       </c>
       <c r="H15" s="8"/>
     </row>
     <row r="16" spans="1:8" ht="51">
-      <c r="A16" s="25"/>
-      <c r="B16" s="28"/>
+      <c r="A16" s="22"/>
+      <c r="B16" s="19"/>
       <c r="C16" s="2" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H16" s="8"/>
     </row>
     <row r="17" spans="1:8" ht="54">
-      <c r="A17" s="25"/>
+      <c r="A17" s="22"/>
       <c r="B17" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E17" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="G17" s="6" t="s">
         <v>63</v>
-      </c>
-      <c r="C17" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="E17" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="G17" s="6" t="s">
-        <v>69</v>
       </c>
       <c r="H17" s="8"/>
     </row>
     <row r="18" spans="1:8" ht="39">
-      <c r="A18" s="25"/>
+      <c r="A18" s="22"/>
       <c r="B18" s="6" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D18" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E18" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="G18" s="6" t="s">
         <v>64</v>
-      </c>
-      <c r="E18" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G18" s="6" t="s">
-        <v>70</v>
       </c>
       <c r="H18" s="8"/>
     </row>
     <row r="19" spans="1:8" ht="51">
-      <c r="A19" s="25"/>
+      <c r="A19" s="22"/>
       <c r="B19" s="6" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="C19" s="15" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="D19" s="15"/>
       <c r="E19" s="11"/>
       <c r="F19" s="2" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="H19" s="8"/>
     </row>
     <row r="20" spans="1:8" ht="64.5">
-      <c r="A20" s="25" t="s">
-        <v>73</v>
-      </c>
-      <c r="B20" s="26" t="s">
-        <v>74</v>
+      <c r="A20" s="22" t="s">
+        <v>67</v>
+      </c>
+      <c r="B20" s="17" t="s">
+        <v>68</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="G20" s="6" t="s">
-        <v>57</v>
+        <v>81</v>
+      </c>
+      <c r="G20" s="16" t="s">
+        <v>84</v>
       </c>
       <c r="H20" s="8"/>
     </row>
-    <row r="21" spans="1:8" ht="51">
-      <c r="A21" s="25"/>
-      <c r="B21" s="27"/>
+    <row r="21" spans="1:8" ht="63.75">
+      <c r="A21" s="22"/>
+      <c r="B21" s="18"/>
       <c r="C21" s="2" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="E21" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="F21" s="2"/>
-      <c r="G21" s="6"/>
+        <v>8</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="G21" s="16" t="s">
+        <v>85</v>
+      </c>
       <c r="H21" s="8"/>
     </row>
-    <row r="22" spans="1:8" ht="25.5">
-      <c r="A22" s="25"/>
-      <c r="B22" s="27"/>
+    <row r="22" spans="1:8" ht="39">
+      <c r="A22" s="22"/>
+      <c r="B22" s="18"/>
       <c r="C22" s="2" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="E22" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="F22" s="2"/>
-      <c r="G22" s="6"/>
+        <v>8</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="G22" s="16" t="s">
+        <v>88</v>
+      </c>
       <c r="H22" s="8"/>
     </row>
-    <row r="23" spans="1:8" ht="51">
-      <c r="A23" s="25"/>
-      <c r="B23" s="27"/>
+    <row r="23" spans="1:8" ht="67.5">
+      <c r="A23" s="22"/>
+      <c r="B23" s="18"/>
       <c r="C23" s="2" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E23" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="F23" s="2"/>
-      <c r="G23" s="6"/>
+        <v>8</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G23" s="16" t="s">
+        <v>90</v>
+      </c>
       <c r="H23" s="8"/>
     </row>
-    <row r="24" spans="1:8" ht="38.25">
-      <c r="A24" s="25"/>
-      <c r="B24" s="27"/>
+    <row r="24" spans="1:8" ht="63.75">
+      <c r="A24" s="22"/>
+      <c r="B24" s="18"/>
       <c r="C24" s="2" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="E24" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="F24" s="2"/>
-      <c r="G24" s="6"/>
+        <v>8</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="G24" s="16" t="s">
+        <v>94</v>
+      </c>
       <c r="H24" s="8"/>
     </row>
-    <row r="25" spans="1:8" ht="25.5">
-      <c r="A25" s="25"/>
-      <c r="B25" s="27"/>
+    <row r="25" spans="1:8" ht="38.25">
+      <c r="A25" s="22"/>
+      <c r="B25" s="18"/>
       <c r="C25" s="2" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="E25" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="F25" s="2"/>
-      <c r="G25" s="6"/>
+        <v>8</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="G25" s="16" t="s">
+        <v>97</v>
+      </c>
       <c r="H25" s="8"/>
     </row>
-    <row r="26" spans="1:8" ht="25.5">
-      <c r="A26" s="25"/>
-      <c r="B26" s="27"/>
+    <row r="26" spans="1:8" ht="38.25">
+      <c r="A26" s="22"/>
+      <c r="B26" s="18"/>
       <c r="C26" s="2" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="E26" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="F26" s="2"/>
-      <c r="G26" s="6"/>
+        <v>8</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="G26" s="16" t="s">
+        <v>107</v>
+      </c>
       <c r="H26" s="8"/>
     </row>
-    <row r="27" spans="1:8" ht="25.5">
-      <c r="A27" s="25"/>
-      <c r="B27" s="27"/>
+    <row r="27" spans="1:8" ht="67.5">
+      <c r="A27" s="22"/>
+      <c r="B27" s="18"/>
       <c r="C27" s="2" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="E27" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="F27" s="2"/>
-      <c r="G27" s="6"/>
+        <v>8</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="G27" s="16" t="s">
+        <v>108</v>
+      </c>
       <c r="H27" s="8"/>
     </row>
-    <row r="28" spans="1:8" ht="25.5">
-      <c r="A28" s="25"/>
-      <c r="B28" s="27"/>
+    <row r="28" spans="1:8" ht="51">
+      <c r="A28" s="22"/>
+      <c r="B28" s="18"/>
       <c r="C28" s="2" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="E28" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="F28" s="2"/>
-      <c r="G28" s="6"/>
+        <v>8</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>110</v>
+      </c>
       <c r="H28" s="8"/>
     </row>
-    <row r="29" spans="1:8" ht="25.5">
-      <c r="A29" s="25"/>
-      <c r="B29" s="28"/>
+    <row r="29" spans="1:8" ht="27">
+      <c r="A29" s="22"/>
+      <c r="B29" s="19"/>
       <c r="C29" s="2" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>86</v>
+        <v>111</v>
       </c>
       <c r="E29" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="F29" s="2"/>
-      <c r="G29" s="6"/>
+        <v>8</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="G29" s="16" t="s">
+        <v>97</v>
+      </c>
       <c r="H29" s="8"/>
     </row>
-    <row r="30" spans="1:8" ht="54">
-      <c r="A30" s="25"/>
-      <c r="B30" s="6" t="s">
-        <v>98</v>
+    <row r="30" spans="1:8" ht="67.5">
+      <c r="A30" s="22"/>
+      <c r="B30" s="16" t="s">
+        <v>115</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>64</v>
+        <v>113</v>
       </c>
       <c r="E30" s="11" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="G30" s="6" t="s">
-        <v>69</v>
+        <v>117</v>
+      </c>
+      <c r="G30" s="16" t="s">
+        <v>118</v>
       </c>
       <c r="H30" s="8"/>
     </row>
-    <row r="31" spans="1:8" ht="39">
-      <c r="A31" s="25"/>
-      <c r="B31" s="6" t="s">
-        <v>99</v>
+    <row r="31" spans="1:8" ht="64.5">
+      <c r="A31" s="22"/>
+      <c r="B31" s="16" t="s">
+        <v>116</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>64</v>
+        <v>113</v>
       </c>
       <c r="E31" s="11" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G31" s="6" t="s">
-        <v>70</v>
+        <v>119</v>
+      </c>
+      <c r="G31" s="16" t="s">
+        <v>120</v>
       </c>
       <c r="H31" s="8"/>
     </row>
-    <row r="32" spans="1:8" ht="53.25">
-      <c r="A32" s="25"/>
-      <c r="B32" s="6" t="s">
-        <v>100</v>
+    <row r="32" spans="1:8" ht="51">
+      <c r="A32" s="22"/>
+      <c r="B32" s="16" t="s">
+        <v>121</v>
       </c>
       <c r="C32" s="15" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="D32" s="15"/>
       <c r="E32" s="11"/>
       <c r="F32" s="2" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>72</v>
+        <v>122</v>
       </c>
       <c r="H32" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="B13:B16"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="A13:A19"/>
     <mergeCell ref="A20:A32"/>
     <mergeCell ref="B20:B29"/>
     <mergeCell ref="B1:B2"/>
@@ -3144,6 +4153,12 @@
     <mergeCell ref="B9:B10"/>
     <mergeCell ref="E9:E10"/>
     <mergeCell ref="B3:B5"/>
+    <mergeCell ref="B13:B16"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="A13:A19"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/internal_doc/05.测试设计/参数校验/元数据参数校验测试设计.xlsx
+++ b/internal_doc/05.测试设计/参数校验/元数据参数校验测试设计.xlsx
@@ -785,13 +785,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">1、不指定ReplSize，默认为1
-2、有效取值：0、-1、7
-取值等于数据组节点个数
-</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <t>1、不指定Compressed，</t>
     </r>
@@ -896,6 +889,13 @@
   </si>
   <si>
     <t>已存在的CL</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">1、不指定ReplSize，默认为1
+2、有效取值：0、-1（当前活动的节点）、7
+取值等于数据组节点个数
+</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1080,7 +1080,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -1124,6 +1124,15 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1135,12 +1144,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1472,48 +1475,48 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" s="9" customFormat="1">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="19" t="s">
+      <c r="B1" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="C1" s="19" t="s">
+      <c r="C1" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="D1" s="21" t="s">
+      <c r="D1" s="22" t="s">
         <v>24</v>
       </c>
-      <c r="E1" s="22"/>
-      <c r="F1" s="19" t="s">
+      <c r="E1" s="23"/>
+      <c r="F1" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="G1" s="19" t="s">
+      <c r="G1" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="H1" s="19" t="s">
+      <c r="H1" s="16" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="2" spans="1:8" s="9" customFormat="1" ht="25.5">
-      <c r="A2" s="20"/>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
+      <c r="A2" s="17"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
       <c r="D2" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F2" s="20"/>
-      <c r="G2" s="20"/>
-      <c r="H2" s="20"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
+      <c r="H2" s="17"/>
     </row>
     <row r="3" spans="1:8" ht="63.75">
-      <c r="A3" s="23" t="s">
+      <c r="A3" s="24" t="s">
         <v>29</v>
       </c>
-      <c r="B3" s="25" t="s">
+      <c r="B3" s="26" t="s">
         <v>30</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -1534,8 +1537,8 @@
       <c r="H3" s="10"/>
     </row>
     <row r="4" spans="1:8" ht="38.25">
-      <c r="A4" s="24"/>
-      <c r="B4" s="25"/>
+      <c r="A4" s="25"/>
+      <c r="B4" s="26"/>
       <c r="C4" s="1" t="s">
         <v>35</v>
       </c>
@@ -1554,8 +1557,8 @@
       <c r="H4" s="10"/>
     </row>
     <row r="5" spans="1:8" ht="38.25">
-      <c r="A5" s="24"/>
-      <c r="B5" s="25"/>
+      <c r="A5" s="25"/>
+      <c r="B5" s="26"/>
       <c r="C5" s="1" t="s">
         <v>36</v>
       </c>
@@ -1574,7 +1577,7 @@
       <c r="H5" s="10"/>
     </row>
     <row r="6" spans="1:8" ht="63.75">
-      <c r="A6" s="24"/>
+      <c r="A6" s="25"/>
       <c r="B6" s="1" t="s">
         <v>39</v>
       </c>
@@ -1596,7 +1599,7 @@
       <c r="H6" s="10"/>
     </row>
     <row r="7" spans="1:8" ht="38.25">
-      <c r="A7" s="24"/>
+      <c r="A7" s="25"/>
       <c r="B7" s="1" t="s">
         <v>40</v>
       </c>
@@ -1618,7 +1621,7 @@
       <c r="H7" s="10"/>
     </row>
     <row r="8" spans="1:8" ht="38.25">
-      <c r="A8" s="24"/>
+      <c r="A8" s="25"/>
       <c r="B8" s="1" t="s">
         <v>41</v>
       </c>
@@ -1636,8 +1639,8 @@
       <c r="H8" s="10"/>
     </row>
     <row r="9" spans="1:8" ht="45.75" customHeight="1">
-      <c r="A9" s="24"/>
-      <c r="B9" s="25" t="s">
+      <c r="A9" s="25"/>
+      <c r="B9" s="26" t="s">
         <v>44</v>
       </c>
       <c r="C9" s="6" t="s">
@@ -1646,7 +1649,7 @@
       <c r="D9" s="14" t="s">
         <v>102</v>
       </c>
-      <c r="E9" s="26" t="s">
+      <c r="E9" s="27" t="s">
         <v>1</v>
       </c>
       <c r="F9" s="14" t="s">
@@ -1658,15 +1661,15 @@
       <c r="H9" s="10"/>
     </row>
     <row r="10" spans="1:8" ht="76.5">
-      <c r="A10" s="24"/>
-      <c r="B10" s="25"/>
+      <c r="A10" s="25"/>
+      <c r="B10" s="26"/>
       <c r="C10" s="6" t="s">
         <v>36</v>
       </c>
       <c r="D10" s="14" t="s">
         <v>104</v>
       </c>
-      <c r="E10" s="27"/>
+      <c r="E10" s="28"/>
       <c r="F10" s="1" t="s">
         <v>38</v>
       </c>
@@ -1676,7 +1679,7 @@
       <c r="H10" s="10"/>
     </row>
     <row r="11" spans="1:8" ht="51">
-      <c r="A11" s="24"/>
+      <c r="A11" s="25"/>
       <c r="B11" s="1" t="s">
         <v>46</v>
       </c>
@@ -1694,7 +1697,7 @@
       <c r="H11" s="10"/>
     </row>
     <row r="12" spans="1:8" ht="51">
-      <c r="A12" s="24"/>
+      <c r="A12" s="25"/>
       <c r="B12" s="8" t="s">
         <v>47</v>
       </c>
@@ -1712,10 +1715,10 @@
       <c r="H12" s="10"/>
     </row>
     <row r="13" spans="1:8" ht="63.75">
-      <c r="A13" s="15" t="s">
+      <c r="A13" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="B13" s="16" t="s">
+      <c r="B13" s="19" t="s">
         <v>49</v>
       </c>
       <c r="C13" s="1" t="s">
@@ -1736,8 +1739,8 @@
       <c r="H13" s="10"/>
     </row>
     <row r="14" spans="1:8" ht="89.25">
-      <c r="A14" s="15"/>
-      <c r="B14" s="17"/>
+      <c r="A14" s="18"/>
+      <c r="B14" s="20"/>
       <c r="C14" s="1" t="s">
         <v>3</v>
       </c>
@@ -1756,8 +1759,8 @@
       <c r="H14" s="10"/>
     </row>
     <row r="15" spans="1:8" ht="38.25">
-      <c r="A15" s="15"/>
-      <c r="B15" s="17"/>
+      <c r="A15" s="18"/>
+      <c r="B15" s="20"/>
       <c r="C15" s="1" t="s">
         <v>4</v>
       </c>
@@ -1776,8 +1779,8 @@
       <c r="H15" s="10"/>
     </row>
     <row r="16" spans="1:8" ht="51">
-      <c r="A16" s="15"/>
-      <c r="B16" s="18"/>
+      <c r="A16" s="18"/>
+      <c r="B16" s="21"/>
       <c r="C16" s="1" t="s">
         <v>6</v>
       </c>
@@ -1796,7 +1799,7 @@
       <c r="H16" s="10"/>
     </row>
     <row r="17" spans="1:8" ht="51">
-      <c r="A17" s="15"/>
+      <c r="A17" s="18"/>
       <c r="B17" s="1" t="s">
         <v>51</v>
       </c>
@@ -1818,7 +1821,7 @@
       <c r="H17" s="10"/>
     </row>
     <row r="18" spans="1:8" ht="38.25">
-      <c r="A18" s="15"/>
+      <c r="A18" s="18"/>
       <c r="B18" s="1" t="s">
         <v>53</v>
       </c>
@@ -1840,7 +1843,7 @@
       <c r="H18" s="10"/>
     </row>
     <row r="19" spans="1:8" ht="51">
-      <c r="A19" s="15"/>
+      <c r="A19" s="18"/>
       <c r="B19" s="1" t="s">
         <v>55</v>
       </c>
@@ -1858,10 +1861,10 @@
       <c r="H19" s="10"/>
     </row>
     <row r="20" spans="1:8" ht="63.75">
-      <c r="A20" s="15" t="s">
+      <c r="A20" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="B20" s="16" t="s">
+      <c r="B20" s="19" t="s">
         <v>56</v>
       </c>
       <c r="C20" s="1" t="s">
@@ -1882,8 +1885,8 @@
       <c r="H20" s="10"/>
     </row>
     <row r="21" spans="1:8" ht="51">
-      <c r="A21" s="15"/>
-      <c r="B21" s="17"/>
+      <c r="A21" s="18"/>
+      <c r="B21" s="20"/>
       <c r="C21" s="6" t="s">
         <v>11</v>
       </c>
@@ -1902,8 +1905,8 @@
       <c r="H21" s="10"/>
     </row>
     <row r="22" spans="1:8" ht="51.75">
-      <c r="A22" s="15"/>
-      <c r="B22" s="17"/>
+      <c r="A22" s="18"/>
+      <c r="B22" s="20"/>
       <c r="C22" s="1" t="s">
         <v>12</v>
       </c>
@@ -1922,8 +1925,8 @@
       <c r="H22" s="10"/>
     </row>
     <row r="23" spans="1:8" ht="76.5">
-      <c r="A23" s="15"/>
-      <c r="B23" s="17"/>
+      <c r="A23" s="18"/>
+      <c r="B23" s="20"/>
       <c r="C23" s="1" t="s">
         <v>13</v>
       </c>
@@ -1942,8 +1945,8 @@
       <c r="H23" s="10"/>
     </row>
     <row r="24" spans="1:8" ht="63.75">
-      <c r="A24" s="15"/>
-      <c r="B24" s="17"/>
+      <c r="A24" s="18"/>
+      <c r="B24" s="20"/>
       <c r="C24" s="1" t="s">
         <v>14</v>
       </c>
@@ -1953,8 +1956,8 @@
       <c r="E24" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="F24" s="14" t="s">
-        <v>114</v>
+      <c r="F24" s="15" t="s">
+        <v>124</v>
       </c>
       <c r="G24" s="14" t="s">
         <v>113</v>
@@ -1962,28 +1965,28 @@
       <c r="H24" s="10"/>
     </row>
     <row r="25" spans="1:8" ht="27.75" customHeight="1">
-      <c r="A25" s="15"/>
-      <c r="B25" s="17"/>
+      <c r="A25" s="18"/>
+      <c r="B25" s="20"/>
       <c r="C25" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D25" s="14" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E25" s="4" t="s">
         <v>37</v>
       </c>
       <c r="F25" s="14" t="s">
+        <v>114</v>
+      </c>
+      <c r="G25" s="14" t="s">
         <v>115</v>
       </c>
-      <c r="G25" s="14" t="s">
-        <v>116</v>
-      </c>
       <c r="H25" s="10"/>
     </row>
     <row r="26" spans="1:8" ht="25.5">
-      <c r="A26" s="15"/>
-      <c r="B26" s="17"/>
+      <c r="A26" s="18"/>
+      <c r="B26" s="20"/>
       <c r="C26" s="1" t="s">
         <v>16</v>
       </c>
@@ -1994,7 +1997,7 @@
         <v>37</v>
       </c>
       <c r="F26" s="14" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G26" s="6" t="s">
         <v>59</v>
@@ -2002,28 +2005,28 @@
       <c r="H26" s="10"/>
     </row>
     <row r="27" spans="1:8" ht="89.25">
-      <c r="A27" s="15"/>
-      <c r="B27" s="17"/>
+      <c r="A27" s="18"/>
+      <c r="B27" s="20"/>
       <c r="C27" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D27" s="14" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E27" s="4" t="s">
         <v>37</v>
       </c>
       <c r="F27" s="14" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G27" s="14" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H27" s="10"/>
     </row>
     <row r="28" spans="1:8" ht="63.75">
-      <c r="A28" s="15"/>
-      <c r="B28" s="17"/>
+      <c r="A28" s="18"/>
+      <c r="B28" s="20"/>
       <c r="C28" s="1" t="s">
         <v>18</v>
       </c>
@@ -2034,7 +2037,7 @@
         <v>37</v>
       </c>
       <c r="F28" s="14" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G28" s="1" t="s">
         <v>61</v>
@@ -2042,8 +2045,8 @@
       <c r="H28" s="10"/>
     </row>
     <row r="29" spans="1:8" ht="25.5">
-      <c r="A29" s="15"/>
-      <c r="B29" s="18"/>
+      <c r="A29" s="18"/>
+      <c r="B29" s="21"/>
       <c r="C29" s="1" t="s">
         <v>19</v>
       </c>
@@ -2062,7 +2065,7 @@
       <c r="H29" s="10"/>
     </row>
     <row r="30" spans="1:8" ht="76.5">
-      <c r="A30" s="15"/>
+      <c r="A30" s="18"/>
       <c r="B30" s="1" t="s">
         <v>63</v>
       </c>
@@ -2076,7 +2079,7 @@
         <v>33</v>
       </c>
       <c r="F30" s="14" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G30" s="1" t="s">
         <v>69</v>
@@ -2084,7 +2087,7 @@
       <c r="H30" s="10"/>
     </row>
     <row r="31" spans="1:8" ht="63.75">
-      <c r="A31" s="15"/>
+      <c r="A31" s="18"/>
       <c r="B31" s="1" t="s">
         <v>65</v>
       </c>
@@ -2098,7 +2101,7 @@
         <v>33</v>
       </c>
       <c r="F31" s="14" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G31" s="1" t="s">
         <v>66</v>
@@ -2106,7 +2109,7 @@
       <c r="H31" s="10"/>
     </row>
     <row r="32" spans="1:8" ht="51">
-      <c r="A32" s="15"/>
+      <c r="A32" s="18"/>
       <c r="B32" s="1" t="s">
         <v>67</v>
       </c>
@@ -2125,11 +2128,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="A13:A19"/>
     <mergeCell ref="A20:A32"/>
     <mergeCell ref="B20:B29"/>
     <mergeCell ref="B1:B2"/>
@@ -2140,6 +2138,11 @@
     <mergeCell ref="E9:E10"/>
     <mergeCell ref="B3:B5"/>
     <mergeCell ref="B13:B16"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="A13:A19"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/internal_doc/05.测试设计/参数校验/元数据参数校验测试设计.xlsx
+++ b/internal_doc/05.测试设计/参数校验/元数据参数校验测试设计.xlsx
@@ -30,10 +30,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>options:PageSize</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>options:Domain</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -43,32 +39,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>options:LobPageSize</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、有效取值：0，4096，8192，16384，32768，65536，131072，262144，524288
-2、不指定LobPageSize</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>1、已存在的CS，非系统CS
-2、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>系统CS（直连编目）</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>1、加条件查询，如：db.listCollectionSpaces(“test”)
 2、空串，如：db.listCollectionSpaces(‘’)</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -111,12 +81,6 @@
   </si>
   <si>
     <t>options:AutoIndexId</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、全局唯一
-2、字符有效，即不为空串且不包含点（.）或$，如：test-123、123、中文名称、-123
-3、有效长度：1B、127B</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -225,12 +189,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>1、Autosplit:true
-   Autosplit:false
-2、不指定AutoSplit</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>dropDomain
 语法：db.dropDomain(&lt; name &gt;)</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -298,10 +256,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>已存在的CS</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>getCS
 语法：db.getCS(&lt; name &gt;)</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -328,12 +282,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>1、不指定shardingType
-2、ShardingType:"hash"
-3、ShardingType:"range"</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>1、取值非法，如test
 2、空串</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -433,16 +381,6 @@
     <t>1、不存在的组
 2、空串
 3、不指定组</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Autosplit:true|false</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、Autosplit:true
-   Autosplit:false
-2、不指定AutoSplit</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -470,11 +408,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>域存在，且非系统域
-系统域</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>1、不存在的域
 3、空串，如db.getDomain(“”)
 4、不指定域，如db.getDomain()</t>
@@ -510,11 +443,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>1、已存在的域，非系统域
-2、不指定域</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>1、不存在的域
 2、系统域
 4、空串</t>
@@ -558,12 +486,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>1、单分区键，取值1|-1
-2、多分区键，取值1|-1
-3、不指定ShardingKey</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <t>1、字段值无效，如ShardingType:"test"
 2、空</t>
@@ -593,23 +515,6 @@
   <si>
     <t xml:space="preserve">hash 分区时填写，代表了 hash 分区的个数。其值必须是2的幂。范围在[2^3, 2^20]，即为8~1048576范围内2的幂次方取值
 </t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>1、hash分区，Partition有效取值：8、1048576
-2、不指定Partition，</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>默认为4096</t>
-    </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -623,71 +528,7 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <t>1、不指定Compressed，</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>默认true</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">
-2、Compressed:true|false</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、全局唯一
-2、字符有效，即不为空串且不包含点（.）或$之外的字符，如：test-123、123、中文名称、-123
-3、有效长度：1B、127B</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>1、存在的组
-2、组个数，如</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>10</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>个</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>不能获取系统域</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>不加条件查询</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -696,45 +537,7 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>存在的组</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>bool:true|false</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、全局唯一
-2、字符有效，即不为空串且不包含点（.）或$，如：test-123、123、中文名称、-123
-3、有效长度：1B、127B</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>1、有效取值：0，4096，8192，16384，32768，65536
-2、db.createCS(&lt; name &gt;,[ PageSize ])方式创建CS，如：db.createCS("testCS",</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>[0,4096]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>)
-3、不指定PageSize，即默认为65536</t>
-    </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -785,72 +588,12 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <t>1、不指定Compressed，</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>默认为false</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">
-2、Compressed:true|false</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>1、取值非法，如test
 2、空串</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>Compressed:true|false</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>1、不指定IsMainCL，</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>默认为false</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">
-2、IsMainCL:true|false</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、ShardingType:"hash"，AutoSplit:true，且不指定Group
-2、AutoSplit:false
-3、域中AutoSplit:true，CL不指定AutoSplit</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -867,35 +610,475 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>1、所属CS指定域，指定CL的Group为CS所属域中的group
-2、所属CS不指定域，指定CL的Group为系统内任意复制组</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>已存在的CL</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>，非系统CS</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>已存在的CL</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve">1、不指定ReplSize，默认为1
 2、有效取值：0、-1（当前活动的节点）、7
 取值等于数据组节点个数
 </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>options:PageSize</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>options:LobPageSize</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>1、全局唯一</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+2、字符有效，即不为空串且不包含点（.）或$之外的字符，如：test-123、123、中文名称、-123
+3、有效长度：1B、127B</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>1、存在的组</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+2、组个数，如</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>个</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Autosplit:true|false，默认为false</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、Autosplit:true
+   Autosplit:false
+2、不指定AutoSplit，默认为false</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>域存在，且非系统域</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+系统域</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>存在的组</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1、Autosplit:true
+   Autosplit:false
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>2、不指定AutoSplit</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>1、全局唯一</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+2、字符有效，即不为空串且不包含点（.）或$，如：test-123、123、中文名称、-123
+3、有效长度：1B、127B</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、已存在的域，非系统域
+2、不指定域</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1、有效取值：0，4096，8192，16384，32768，65536，131072，262144，524288
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>2、不指定LobPageSize</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1、有效取值：0，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>4096</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>，8192，16384，32768，65536
+2、db.createCS(&lt; name &gt;,[ PageSize ])方式创建CS，如：db.createCS("testCS",</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>[0,4096]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>3、不指定PageSize，即默认为65536</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>已存在的CS</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>1、已存在的CS，非系统CS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+2、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>系统CS（直连编目）</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>不加条件查询</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">1、单分区键，取值1|-1
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>2、多分区键，取值1|-1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+3、不指定ShardingKey</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1、不指定shardingType
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>2、ShardingType:"hash"
+3、ShardingType:"range"</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1、hash分区，Partition有效取值：8、1048576
+2、不指定Partition，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>默认为4096</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、不指定Compressed，默认为false
+2、Compressed:true|false</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、不指定IsMainCL，默认为false
+2、IsMainCL:true|false</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、ShardingType:"hash"，AutoSplit:true，且不指定Group
+2、AutoSplit:false
+3、域中AutoSplit:true，CL不指定AutoSplit</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>1、所属CS指定域，指定CL的Group为CS所属域中的group</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+2、所属CS不指定域，指定CL的Group为系统内任意复制组</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>1、不指定Compressed，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>默认true</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>2、Compressed:true|false</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>已存在的CL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>，非系统CS</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>已存在的CL</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>不加条件查询</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -903,7 +1086,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -971,6 +1154,13 @@
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color rgb="FF0000FF"/>
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
@@ -1080,7 +1270,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -1127,24 +1317,24 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1165,6 +1355,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1172,6 +1365,11 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FF0000FF"/>
+    </mruColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -1475,64 +1673,64 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" s="9" customFormat="1">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" s="22" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1" s="23"/>
+      <c r="F1" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="16" t="s">
+    </row>
+    <row r="2" spans="1:8" s="9" customFormat="1" ht="25.5">
+      <c r="A2" s="21"/>
+      <c r="B2" s="21"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C1" s="16" t="s">
+      <c r="E2" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D1" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="E1" s="23"/>
-      <c r="F1" s="16" t="s">
-        <v>25</v>
-      </c>
-      <c r="G1" s="16" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="16" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" s="9" customFormat="1" ht="25.5">
-      <c r="A2" s="17"/>
-      <c r="B2" s="17"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F2" s="17"/>
-      <c r="G2" s="17"/>
-      <c r="H2" s="17"/>
+      <c r="F2" s="21"/>
+      <c r="G2" s="21"/>
+      <c r="H2" s="21"/>
     </row>
     <row r="3" spans="1:8" ht="63.75">
       <c r="A3" s="24" t="s">
+        <v>24</v>
+      </c>
+      <c r="B3" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F3" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="G3" s="6" t="s">
         <v>29</v>
-      </c>
-      <c r="B3" s="26" t="s">
-        <v>30</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="F3" s="14" t="s">
-        <v>98</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>34</v>
       </c>
       <c r="H3" s="10"/>
     </row>
@@ -1540,19 +1738,19 @@
       <c r="A4" s="25"/>
       <c r="B4" s="26"/>
       <c r="C4" s="1" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="F4" s="14" t="s">
-        <v>99</v>
+        <v>28</v>
+      </c>
+      <c r="F4" s="15" t="s">
+        <v>101</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="H4" s="10"/>
     </row>
@@ -1560,103 +1758,103 @@
       <c r="A5" s="25"/>
       <c r="B5" s="26"/>
       <c r="C5" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>72</v>
+        <v>31</v>
+      </c>
+      <c r="D5" s="15" t="s">
+        <v>102</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>73</v>
+        <v>32</v>
+      </c>
+      <c r="F5" s="29" t="s">
+        <v>103</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="H5" s="10"/>
     </row>
     <row r="6" spans="1:8" ht="63.75">
       <c r="A6" s="25"/>
       <c r="B6" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>76</v>
+        <v>28</v>
+      </c>
+      <c r="F6" s="29" t="s">
+        <v>66</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="H6" s="10"/>
     </row>
     <row r="7" spans="1:8" ht="38.25">
       <c r="A7" s="25"/>
       <c r="B7" s="1" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>100</v>
+        <v>83</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>78</v>
+        <v>28</v>
+      </c>
+      <c r="F7" s="15" t="s">
+        <v>104</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="H7" s="10"/>
     </row>
     <row r="8" spans="1:8" ht="38.25">
       <c r="A8" s="25"/>
       <c r="B8" s="1" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="D8" s="5"/>
       <c r="E8" s="4"/>
-      <c r="F8" s="14" t="s">
-        <v>101</v>
+      <c r="F8" s="29" t="s">
+        <v>37</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="H8" s="10"/>
     </row>
     <row r="9" spans="1:8" ht="45.75" customHeight="1">
       <c r="A9" s="25"/>
       <c r="B9" s="26" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>102</v>
+        <v>84</v>
       </c>
       <c r="E9" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="F9" s="14" t="s">
-        <v>103</v>
+      <c r="F9" s="29" t="s">
+        <v>105</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="H9" s="10"/>
     </row>
@@ -1664,470 +1862,475 @@
       <c r="A10" s="25"/>
       <c r="B10" s="26"/>
       <c r="C10" s="6" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>104</v>
+        <v>85</v>
       </c>
       <c r="E10" s="28"/>
-      <c r="F10" s="1" t="s">
-        <v>38</v>
+      <c r="F10" s="15" t="s">
+        <v>106</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="H10" s="10"/>
     </row>
     <row r="11" spans="1:8" ht="51">
       <c r="A11" s="25"/>
       <c r="B11" s="1" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="D11" s="7"/>
       <c r="E11" s="4"/>
-      <c r="F11" s="14" t="s">
-        <v>101</v>
+      <c r="F11" s="29" t="s">
+        <v>37</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="H11" s="10"/>
     </row>
     <row r="12" spans="1:8" ht="51">
       <c r="A12" s="25"/>
       <c r="B12" s="8" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="D12" s="7"/>
       <c r="E12" s="4"/>
-      <c r="F12" s="14" t="s">
-        <v>101</v>
+      <c r="F12" s="29" t="s">
+        <v>37</v>
       </c>
       <c r="G12" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H12" s="10"/>
+    </row>
+    <row r="13" spans="1:8" ht="63.75">
+      <c r="A13" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="B13" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F13" s="15" t="s">
+        <v>107</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="H13" s="10"/>
+    </row>
+    <row r="14" spans="1:8" ht="89.25">
+      <c r="A14" s="16"/>
+      <c r="B14" s="18"/>
+      <c r="C14" s="15" t="s">
+        <v>98</v>
+      </c>
+      <c r="D14" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="F14" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="G14" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="H14" s="10"/>
+    </row>
+    <row r="15" spans="1:8" ht="38.25">
+      <c r="A15" s="16"/>
+      <c r="B15" s="18"/>
+      <c r="C15" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="F15" s="29" t="s">
+        <v>108</v>
+      </c>
+      <c r="G15" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="H15" s="10"/>
+    </row>
+    <row r="16" spans="1:8" ht="51">
+      <c r="A16" s="16"/>
+      <c r="B16" s="19"/>
+      <c r="C16" s="15" t="s">
+        <v>99</v>
+      </c>
+      <c r="D16" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="F16" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="G16" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="H16" s="10"/>
+    </row>
+    <row r="17" spans="1:8" ht="51">
+      <c r="A17" s="16"/>
+      <c r="B17" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F17" s="29" t="s">
+        <v>111</v>
+      </c>
+      <c r="G17" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H17" s="10"/>
+    </row>
+    <row r="18" spans="1:8" ht="38.25">
+      <c r="A18" s="16"/>
+      <c r="B18" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D18" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F18" s="15" t="s">
+        <v>112</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H18" s="10"/>
+    </row>
+    <row r="19" spans="1:8" ht="51">
+      <c r="A19" s="16"/>
+      <c r="B19" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="H12" s="10"/>
-    </row>
-    <row r="13" spans="1:8" ht="63.75">
-      <c r="A13" s="18" t="s">
-        <v>2</v>
-      </c>
-      <c r="B13" s="19" t="s">
-        <v>49</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E13" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="F13" s="14" t="s">
-        <v>105</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="H13" s="10"/>
-    </row>
-    <row r="14" spans="1:8" ht="89.25">
-      <c r="A14" s="18"/>
-      <c r="B14" s="20"/>
-      <c r="C14" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D14" s="14" t="s">
-        <v>107</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="F14" s="14" t="s">
-        <v>106</v>
-      </c>
-      <c r="G14" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="H14" s="10"/>
-    </row>
-    <row r="15" spans="1:8" ht="38.25">
-      <c r="A15" s="18"/>
-      <c r="B15" s="20"/>
-      <c r="C15" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D15" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="E15" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="F15" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="G15" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="H15" s="10"/>
-    </row>
-    <row r="16" spans="1:8" ht="51">
-      <c r="A16" s="18"/>
-      <c r="B16" s="21"/>
-      <c r="C16" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D16" s="14" t="s">
-        <v>88</v>
-      </c>
-      <c r="E16" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="G16" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="H16" s="10"/>
-    </row>
-    <row r="17" spans="1:8" ht="51">
-      <c r="A17" s="18"/>
-      <c r="B17" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D17" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="E17" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="F17" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="G17" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="H17" s="10"/>
-    </row>
-    <row r="18" spans="1:8" ht="38.25">
-      <c r="A18" s="18"/>
-      <c r="B18" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D18" s="14" t="s">
-        <v>108</v>
-      </c>
-      <c r="E18" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G18" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="H18" s="10"/>
-    </row>
-    <row r="19" spans="1:8" ht="51">
-      <c r="A19" s="18"/>
-      <c r="B19" s="1" t="s">
-        <v>55</v>
-      </c>
       <c r="C19" s="5" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="D19" s="5"/>
       <c r="E19" s="4"/>
-      <c r="F19" s="1" t="s">
-        <v>43</v>
+      <c r="F19" s="29" t="s">
+        <v>113</v>
       </c>
       <c r="G19" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H19" s="10"/>
+    </row>
+    <row r="20" spans="1:8" ht="63.75">
+      <c r="A20" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="B20" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D20" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F20" s="15" t="s">
+        <v>107</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="H20" s="10"/>
+    </row>
+    <row r="21" spans="1:8" ht="51">
+      <c r="A21" s="16"/>
+      <c r="B21" s="18"/>
+      <c r="C21" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D21" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="F21" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="G21" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="H21" s="10"/>
+    </row>
+    <row r="22" spans="1:8" ht="51.75">
+      <c r="A22" s="16"/>
+      <c r="B22" s="18"/>
+      <c r="C22" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D22" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="F22" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="G22" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="H22" s="10"/>
+    </row>
+    <row r="23" spans="1:8" ht="76.5">
+      <c r="A23" s="16"/>
+      <c r="B23" s="18"/>
+      <c r="C23" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="H19" s="10"/>
-    </row>
-    <row r="20" spans="1:8" ht="63.75">
-      <c r="A20" s="18" t="s">
+      <c r="D23" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="F23" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="G23" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="H23" s="10"/>
+    </row>
+    <row r="24" spans="1:8" ht="63.75">
+      <c r="A24" s="16"/>
+      <c r="B24" s="18"/>
+      <c r="C24" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B20" s="19" t="s">
+      <c r="D24" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="F24" s="29" t="s">
+        <v>97</v>
+      </c>
+      <c r="G24" s="14" t="s">
+        <v>92</v>
+      </c>
+      <c r="H24" s="10"/>
+    </row>
+    <row r="25" spans="1:8" ht="27.75" customHeight="1">
+      <c r="A25" s="16"/>
+      <c r="B25" s="18"/>
+      <c r="C25" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D25" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="F25" s="29" t="s">
+        <v>117</v>
+      </c>
+      <c r="G25" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="H25" s="10"/>
+    </row>
+    <row r="26" spans="1:8" ht="25.5">
+      <c r="A26" s="16"/>
+      <c r="B26" s="18"/>
+      <c r="C26" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D26" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="F26" s="29" t="s">
+        <v>118</v>
+      </c>
+      <c r="G26" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="H26" s="10"/>
+    </row>
+    <row r="27" spans="1:8" ht="89.25">
+      <c r="A27" s="16"/>
+      <c r="B27" s="18"/>
+      <c r="C27" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D27" s="14" t="s">
+        <v>95</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="F27" s="29" t="s">
+        <v>119</v>
+      </c>
+      <c r="G27" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="H27" s="10"/>
+    </row>
+    <row r="28" spans="1:8" ht="63.75">
+      <c r="A28" s="16"/>
+      <c r="B28" s="18"/>
+      <c r="C28" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="F28" s="15" t="s">
+        <v>120</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="H28" s="10"/>
+    </row>
+    <row r="29" spans="1:8" ht="25.5">
+      <c r="A29" s="16"/>
+      <c r="B29" s="19"/>
+      <c r="C29" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="F29" s="15" t="s">
+        <v>121</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H29" s="10"/>
+    </row>
+    <row r="30" spans="1:8" ht="76.5">
+      <c r="A30" s="16"/>
+      <c r="B30" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D30" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="C20" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D20" s="14" t="s">
-        <v>109</v>
-      </c>
-      <c r="E20" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="F20" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G20" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="H20" s="10"/>
-    </row>
-    <row r="21" spans="1:8" ht="51">
-      <c r="A21" s="18"/>
-      <c r="B21" s="20"/>
-      <c r="C21" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D21" s="14" t="s">
-        <v>111</v>
-      </c>
-      <c r="E21" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="F21" s="14" t="s">
-        <v>91</v>
-      </c>
-      <c r="G21" s="14" t="s">
-        <v>110</v>
-      </c>
-      <c r="H21" s="10"/>
-    </row>
-    <row r="22" spans="1:8" ht="51.75">
-      <c r="A22" s="18"/>
-      <c r="B22" s="20"/>
-      <c r="C22" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D22" s="14" t="s">
+      <c r="E30" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F30" s="15" t="s">
+        <v>122</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="H30" s="10"/>
+    </row>
+    <row r="31" spans="1:8" ht="63.75">
+      <c r="A31" s="16"/>
+      <c r="B31" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="E22" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="F22" s="6" t="s">
+      <c r="C31" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F31" s="29" t="s">
+        <v>123</v>
+      </c>
+      <c r="G31" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="G22" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="H22" s="10"/>
-    </row>
-    <row r="23" spans="1:8" ht="76.5">
-      <c r="A23" s="18"/>
-      <c r="B23" s="20"/>
-      <c r="C23" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D23" s="14" t="s">
-        <v>93</v>
-      </c>
-      <c r="E23" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="F23" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="G23" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="H23" s="10"/>
-    </row>
-    <row r="24" spans="1:8" ht="63.75">
-      <c r="A24" s="18"/>
-      <c r="B24" s="20"/>
-      <c r="C24" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D24" s="14" t="s">
-        <v>112</v>
-      </c>
-      <c r="E24" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="F24" s="15" t="s">
-        <v>124</v>
-      </c>
-      <c r="G24" s="14" t="s">
-        <v>113</v>
-      </c>
-      <c r="H24" s="10"/>
-    </row>
-    <row r="25" spans="1:8" ht="27.75" customHeight="1">
-      <c r="A25" s="18"/>
-      <c r="B25" s="20"/>
-      <c r="C25" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D25" s="14" t="s">
-        <v>116</v>
-      </c>
-      <c r="E25" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="F25" s="14" t="s">
-        <v>114</v>
-      </c>
-      <c r="G25" s="14" t="s">
-        <v>115</v>
-      </c>
-      <c r="H25" s="10"/>
-    </row>
-    <row r="26" spans="1:8" ht="25.5">
-      <c r="A26" s="18"/>
-      <c r="B26" s="20"/>
-      <c r="C26" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D26" s="14" t="s">
-        <v>60</v>
-      </c>
-      <c r="E26" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="F26" s="14" t="s">
-        <v>117</v>
-      </c>
-      <c r="G26" s="6" t="s">
+      <c r="H31" s="10"/>
+    </row>
+    <row r="32" spans="1:8" ht="51">
+      <c r="A32" s="16"/>
+      <c r="B32" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="H26" s="10"/>
-    </row>
-    <row r="27" spans="1:8" ht="89.25">
-      <c r="A27" s="18"/>
-      <c r="B27" s="20"/>
-      <c r="C27" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D27" s="14" t="s">
-        <v>119</v>
-      </c>
-      <c r="E27" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="F27" s="14" t="s">
-        <v>118</v>
-      </c>
-      <c r="G27" s="14" t="s">
-        <v>120</v>
-      </c>
-      <c r="H27" s="10"/>
-    </row>
-    <row r="28" spans="1:8" ht="63.75">
-      <c r="A28" s="18"/>
-      <c r="B28" s="20"/>
-      <c r="C28" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D28" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="E28" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="F28" s="14" t="s">
-        <v>121</v>
-      </c>
-      <c r="G28" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="H28" s="10"/>
-    </row>
-    <row r="29" spans="1:8" ht="25.5">
-      <c r="A29" s="18"/>
-      <c r="B29" s="21"/>
-      <c r="C29" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="E29" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="F29" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="G29" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="H29" s="10"/>
-    </row>
-    <row r="30" spans="1:8" ht="76.5">
-      <c r="A30" s="18"/>
-      <c r="B30" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="E30" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="F30" s="14" t="s">
-        <v>122</v>
-      </c>
-      <c r="G30" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="H30" s="10"/>
-    </row>
-    <row r="31" spans="1:8" ht="63.75">
-      <c r="A31" s="18"/>
-      <c r="B31" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="E31" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="F31" s="14" t="s">
-        <v>123</v>
-      </c>
-      <c r="G31" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="H31" s="10"/>
-    </row>
-    <row r="32" spans="1:8" ht="51">
-      <c r="A32" s="18"/>
-      <c r="B32" s="1" t="s">
-        <v>67</v>
-      </c>
       <c r="C32" s="5" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="D32" s="5"/>
       <c r="E32" s="4"/>
-      <c r="F32" s="14" t="s">
-        <v>101</v>
+      <c r="F32" s="29" t="s">
+        <v>124</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="H32" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="A13:A19"/>
     <mergeCell ref="A20:A32"/>
     <mergeCell ref="B20:B29"/>
     <mergeCell ref="B1:B2"/>
@@ -2138,11 +2341,6 @@
     <mergeCell ref="E9:E10"/>
     <mergeCell ref="B3:B5"/>
     <mergeCell ref="B13:B16"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="A13:A19"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/internal_doc/05.测试设计/参数校验/元数据参数校验测试设计.xlsx
+++ b/internal_doc/05.测试设计/参数校验/元数据参数校验测试设计.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="126">
   <si>
     <t>无效数据</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -120,82 +120,19 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>createDomain
-语法：db.createDomain(&lt; name &gt;,&lt; groups &gt;,[ options ])</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>name</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">string，全局唯一
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>有效字符是？？有效长度是？？
-参考createCS：不能是空串，含点（.）或者美元符号（$）。且长度不超过127B</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>是</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>1、名称重复</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">
-2、字符无效：包含（.）包含$
-3、无效长度：空串、128B
-4、不指定name
-5、格式错误，如：不带引号输入</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>groups</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>options:Autosplit</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>否</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>dropDomain
-语法：db.dropDomain(&lt; name &gt;)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>getDomain
-语法：db.getDomain(&lt; name &gt;)</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -395,11 +332,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>1、域存在，且非系统域
-2、空域</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>1、不存在的域
 2、域非空，如：域包含CS或CL
 3、系统域
@@ -704,30 +636,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>域存在，且非系统域</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">
-系统域</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>存在的组</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1079,6 +987,121 @@
   </si>
   <si>
     <t>不加条件查询</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>createDomain
+语法：db.createDomain(&lt; name &gt;,&lt; groups &gt;,[ options ])</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">string，全局唯一
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>有效字符是？？有效长度是？？
+参考createCS：name不能是空串，含点（.）或者美元符号（$）。且长度不超过127B</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>groups</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>options:Autosplit</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>getDomain
+语法：db.getDomain(&lt; name &gt;)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>dropDomain
+语法：db.dropDomain(&lt; name &gt;)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>1、名称重复</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+2、字符无效：包含（.）包含$
+3、无效长度：空串、128B
+4、不指定name</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+5、格式错误，如：不带引号输入（公共）</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>域存在，空域，且非系统域</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>域存在，且非系统域</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>系统域  --get显示不出来</t>
+    </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1270,7 +1293,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -1317,6 +1340,18 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1329,12 +1364,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1355,9 +1384,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1673,385 +1699,385 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" s="9" customFormat="1">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="20" t="s">
+      <c r="B1" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="C1" s="20" t="s">
+      <c r="C1" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="D1" s="22" t="s">
+      <c r="D1" s="24" t="s">
         <v>19</v>
       </c>
-      <c r="E1" s="23"/>
-      <c r="F1" s="20" t="s">
+      <c r="E1" s="25"/>
+      <c r="F1" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="G1" s="20" t="s">
+      <c r="G1" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="H1" s="20" t="s">
+      <c r="H1" s="18" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:8" s="9" customFormat="1" ht="25.5">
-      <c r="A2" s="21"/>
-      <c r="B2" s="21"/>
-      <c r="C2" s="21"/>
+      <c r="A2" s="19"/>
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
       <c r="D2" s="2" t="s">
         <v>22</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="F2" s="21"/>
-      <c r="G2" s="21"/>
-      <c r="H2" s="21"/>
-    </row>
-    <row r="3" spans="1:8" ht="63.75">
-      <c r="A3" s="24" t="s">
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
+      <c r="H2" s="19"/>
+    </row>
+    <row r="3" spans="1:8" ht="76.5">
+      <c r="A3" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="B3" s="26" t="s">
+      <c r="B3" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="D3" s="16" t="s">
+        <v>118</v>
+      </c>
+      <c r="E3" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E3" s="4" t="s">
+      <c r="F3" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="G3" s="16" t="s">
+        <v>123</v>
+      </c>
+      <c r="H3" s="10"/>
+    </row>
+    <row r="4" spans="1:8" ht="38.25">
+      <c r="A4" s="27"/>
+      <c r="B4" s="28"/>
+      <c r="C4" s="16" t="s">
+        <v>119</v>
+      </c>
+      <c r="D4" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F4" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="G4" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="H4" s="10"/>
+    </row>
+    <row r="5" spans="1:8" ht="38.25">
+      <c r="A5" s="27"/>
+      <c r="B5" s="28"/>
+      <c r="C5" s="16" t="s">
+        <v>120</v>
+      </c>
+      <c r="D5" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="E5" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="F3" s="15" t="s">
-        <v>100</v>
-      </c>
-      <c r="G3" s="6" t="s">
+      <c r="F5" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="H5" s="10"/>
+    </row>
+    <row r="6" spans="1:8" ht="63.75">
+      <c r="A6" s="27"/>
+      <c r="B6" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F6" s="17" t="s">
+        <v>124</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="H6" s="10"/>
+    </row>
+    <row r="7" spans="1:8" ht="38.25">
+      <c r="A7" s="27"/>
+      <c r="B7" s="16" t="s">
+        <v>121</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F7" s="16" t="s">
+        <v>125</v>
+      </c>
+      <c r="G7" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="H7" s="10"/>
+    </row>
+    <row r="8" spans="1:8" ht="38.25">
+      <c r="A8" s="27"/>
+      <c r="B8" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="H3" s="10"/>
-    </row>
-    <row r="4" spans="1:8" ht="38.25">
-      <c r="A4" s="25"/>
-      <c r="B4" s="26"/>
-      <c r="C4" s="1" t="s">
+      <c r="C8" s="5" t="s">
         <v>30</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="F4" s="15" t="s">
-        <v>101</v>
-      </c>
-      <c r="G4" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="H4" s="10"/>
-    </row>
-    <row r="5" spans="1:8" ht="38.25">
-      <c r="A5" s="25"/>
-      <c r="B5" s="26"/>
-      <c r="C5" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D5" s="15" t="s">
-        <v>102</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="F5" s="29" t="s">
-        <v>103</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H5" s="10"/>
-    </row>
-    <row r="6" spans="1:8" ht="63.75">
-      <c r="A6" s="25"/>
-      <c r="B6" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="D6" s="14" t="s">
-        <v>65</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="F6" s="29" t="s">
-        <v>66</v>
-      </c>
-      <c r="G6" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="H6" s="10"/>
-    </row>
-    <row r="7" spans="1:8" ht="38.25">
-      <c r="A7" s="25"/>
-      <c r="B7" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D7" s="14" t="s">
-        <v>83</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="F7" s="15" t="s">
-        <v>104</v>
-      </c>
-      <c r="G7" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="H7" s="10"/>
-    </row>
-    <row r="8" spans="1:8" ht="38.25">
-      <c r="A8" s="25"/>
-      <c r="B8" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>36</v>
       </c>
       <c r="D8" s="5"/>
       <c r="E8" s="4"/>
-      <c r="F8" s="29" t="s">
-        <v>37</v>
+      <c r="F8" s="17" t="s">
+        <v>31</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="H8" s="10"/>
     </row>
     <row r="9" spans="1:8" ht="45.75" customHeight="1">
-      <c r="A9" s="25"/>
-      <c r="B9" s="26" t="s">
-        <v>38</v>
+      <c r="A9" s="27"/>
+      <c r="B9" s="28" t="s">
+        <v>32</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>84</v>
-      </c>
-      <c r="E9" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="E9" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="F9" s="29" t="s">
-        <v>105</v>
+      <c r="F9" s="17" t="s">
+        <v>97</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="H9" s="10"/>
     </row>
     <row r="10" spans="1:8" ht="76.5">
-      <c r="A10" s="25"/>
-      <c r="B10" s="26"/>
+      <c r="A10" s="27"/>
+      <c r="B10" s="28"/>
       <c r="C10" s="6" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>85</v>
-      </c>
-      <c r="E10" s="28"/>
+        <v>78</v>
+      </c>
+      <c r="E10" s="30"/>
       <c r="F10" s="15" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="H10" s="10"/>
     </row>
     <row r="11" spans="1:8" ht="51">
-      <c r="A11" s="25"/>
+      <c r="A11" s="27"/>
       <c r="B11" s="1" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="D11" s="7"/>
       <c r="E11" s="4"/>
-      <c r="F11" s="29" t="s">
-        <v>37</v>
+      <c r="F11" s="17" t="s">
+        <v>31</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="H11" s="10"/>
     </row>
     <row r="12" spans="1:8" ht="51">
-      <c r="A12" s="25"/>
+      <c r="A12" s="27"/>
       <c r="B12" s="8" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="D12" s="7"/>
       <c r="E12" s="4"/>
-      <c r="F12" s="29" t="s">
+      <c r="F12" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="H12" s="10"/>
+    </row>
+    <row r="13" spans="1:8" ht="63.75">
+      <c r="A13" s="20" t="s">
+        <v>2</v>
+      </c>
+      <c r="B13" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="G12" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="H12" s="10"/>
-    </row>
-    <row r="13" spans="1:8" ht="63.75">
-      <c r="A13" s="16" t="s">
-        <v>2</v>
-      </c>
-      <c r="B13" s="17" t="s">
-        <v>43</v>
-      </c>
       <c r="C13" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>4</v>
       </c>
       <c r="E13" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F13" s="15" t="s">
+        <v>99</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="H13" s="10"/>
+    </row>
+    <row r="14" spans="1:8" ht="89.25">
+      <c r="A14" s="20"/>
+      <c r="B14" s="22"/>
+      <c r="C14" s="15" t="s">
+        <v>91</v>
+      </c>
+      <c r="D14" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="E14" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="F13" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="H13" s="10"/>
-    </row>
-    <row r="14" spans="1:8" ht="89.25">
-      <c r="A14" s="16"/>
-      <c r="B14" s="18"/>
-      <c r="C14" s="15" t="s">
-        <v>98</v>
-      </c>
-      <c r="D14" s="14" t="s">
-        <v>86</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>32</v>
-      </c>
       <c r="F14" s="15" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="H14" s="10"/>
     </row>
     <row r="15" spans="1:8" ht="38.25">
-      <c r="A15" s="16"/>
-      <c r="B15" s="18"/>
+      <c r="A15" s="20"/>
+      <c r="B15" s="22"/>
       <c r="C15" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="F15" s="29" t="s">
-        <v>108</v>
+        <v>28</v>
+      </c>
+      <c r="F15" s="17" t="s">
+        <v>100</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="H15" s="10"/>
     </row>
     <row r="16" spans="1:8" ht="51">
-      <c r="A16" s="16"/>
-      <c r="B16" s="19"/>
+      <c r="A16" s="20"/>
+      <c r="B16" s="23"/>
       <c r="C16" s="15" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="D16" s="14" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="F16" s="15" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="H16" s="10"/>
     </row>
     <row r="17" spans="1:8" ht="51">
-      <c r="A17" s="16"/>
+      <c r="A17" s="20"/>
       <c r="B17" s="1" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="C17" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="E17" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="D17" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="E17" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="F17" s="29" t="s">
-        <v>111</v>
+      <c r="F17" s="17" t="s">
+        <v>103</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="H17" s="10"/>
     </row>
     <row r="18" spans="1:8" ht="38.25">
-      <c r="A18" s="16"/>
+      <c r="A18" s="20"/>
       <c r="B18" s="1" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="C18" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D18" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="E18" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="D18" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="E18" s="4" t="s">
-        <v>28</v>
-      </c>
       <c r="F18" s="15" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="H18" s="10"/>
     </row>
     <row r="19" spans="1:8" ht="51">
-      <c r="A19" s="16"/>
+      <c r="A19" s="20"/>
       <c r="B19" s="1" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="D19" s="5"/>
       <c r="E19" s="4"/>
-      <c r="F19" s="29" t="s">
-        <v>113</v>
+      <c r="F19" s="17" t="s">
+        <v>105</v>
       </c>
       <c r="G19" s="1" t="s">
         <v>5</v>
@@ -2059,278 +2085,273 @@
       <c r="H19" s="10"/>
     </row>
     <row r="20" spans="1:8" ht="63.75">
-      <c r="A20" s="16" t="s">
+      <c r="A20" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="B20" s="17" t="s">
-        <v>49</v>
+      <c r="B20" s="21" t="s">
+        <v>43</v>
       </c>
       <c r="C20" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D20" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="E20" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="D20" s="14" t="s">
-        <v>88</v>
-      </c>
-      <c r="E20" s="4" t="s">
-        <v>28</v>
-      </c>
       <c r="F20" s="15" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="H20" s="10"/>
     </row>
     <row r="21" spans="1:8" ht="51">
-      <c r="A21" s="16"/>
-      <c r="B21" s="18"/>
+      <c r="A21" s="20"/>
+      <c r="B21" s="22"/>
       <c r="C21" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D21" s="14" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="F21" s="15" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="G21" s="14" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="H21" s="10"/>
     </row>
     <row r="22" spans="1:8" ht="51.75">
-      <c r="A22" s="16"/>
-      <c r="B22" s="18"/>
+      <c r="A22" s="20"/>
+      <c r="B22" s="22"/>
       <c r="C22" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D22" s="14" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="F22" s="15" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="H22" s="10"/>
     </row>
     <row r="23" spans="1:8" ht="76.5">
-      <c r="A23" s="16"/>
-      <c r="B23" s="18"/>
+      <c r="A23" s="20"/>
+      <c r="B23" s="22"/>
       <c r="C23" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D23" s="14" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="F23" s="15" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="H23" s="10"/>
     </row>
     <row r="24" spans="1:8" ht="63.75">
-      <c r="A24" s="16"/>
-      <c r="B24" s="18"/>
+      <c r="A24" s="20"/>
+      <c r="B24" s="22"/>
       <c r="C24" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D24" s="14" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="F24" s="29" t="s">
-        <v>97</v>
+        <v>28</v>
+      </c>
+      <c r="F24" s="17" t="s">
+        <v>90</v>
       </c>
       <c r="G24" s="14" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="H24" s="10"/>
     </row>
     <row r="25" spans="1:8" ht="27.75" customHeight="1">
-      <c r="A25" s="16"/>
-      <c r="B25" s="18"/>
+      <c r="A25" s="20"/>
+      <c r="B25" s="22"/>
       <c r="C25" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D25" s="14" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="F25" s="29" t="s">
-        <v>117</v>
+        <v>28</v>
+      </c>
+      <c r="F25" s="17" t="s">
+        <v>109</v>
       </c>
       <c r="G25" s="14" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="H25" s="10"/>
     </row>
     <row r="26" spans="1:8" ht="25.5">
-      <c r="A26" s="16"/>
-      <c r="B26" s="18"/>
+      <c r="A26" s="20"/>
+      <c r="B26" s="22"/>
       <c r="C26" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D26" s="14" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="F26" s="29" t="s">
-        <v>118</v>
+        <v>28</v>
+      </c>
+      <c r="F26" s="17" t="s">
+        <v>110</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="H26" s="10"/>
     </row>
     <row r="27" spans="1:8" ht="89.25">
-      <c r="A27" s="16"/>
-      <c r="B27" s="18"/>
+      <c r="A27" s="20"/>
+      <c r="B27" s="22"/>
       <c r="C27" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D27" s="14" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="F27" s="29" t="s">
-        <v>119</v>
+        <v>28</v>
+      </c>
+      <c r="F27" s="17" t="s">
+        <v>111</v>
       </c>
       <c r="G27" s="14" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="H27" s="10"/>
     </row>
     <row r="28" spans="1:8" ht="63.75">
-      <c r="A28" s="16"/>
-      <c r="B28" s="18"/>
+      <c r="A28" s="20"/>
+      <c r="B28" s="22"/>
       <c r="C28" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="F28" s="15" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="H28" s="10"/>
     </row>
     <row r="29" spans="1:8" ht="25.5">
-      <c r="A29" s="16"/>
-      <c r="B29" s="19"/>
+      <c r="A29" s="20"/>
+      <c r="B29" s="23"/>
       <c r="C29" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="F29" s="15" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="G29" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H29" s="10"/>
+    </row>
+    <row r="30" spans="1:8" ht="76.5">
+      <c r="A30" s="20"/>
+      <c r="B30" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F30" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="H30" s="10"/>
+    </row>
+    <row r="31" spans="1:8" ht="63.75">
+      <c r="A31" s="20"/>
+      <c r="B31" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="H29" s="10"/>
-    </row>
-    <row r="30" spans="1:8" ht="76.5">
-      <c r="A30" s="16"/>
-      <c r="B30" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="C30" s="1" t="s">
+      <c r="C31" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E31" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="D30" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="E30" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="F30" s="15" t="s">
-        <v>122</v>
-      </c>
-      <c r="G30" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="H30" s="10"/>
-    </row>
-    <row r="31" spans="1:8" ht="63.75">
-      <c r="A31" s="16"/>
-      <c r="B31" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="E31" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="F31" s="29" t="s">
-        <v>123</v>
+      <c r="F31" s="17" t="s">
+        <v>115</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="H31" s="10"/>
     </row>
     <row r="32" spans="1:8" ht="51">
-      <c r="A32" s="16"/>
+      <c r="A32" s="20"/>
       <c r="B32" s="1" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="D32" s="5"/>
       <c r="E32" s="4"/>
-      <c r="F32" s="29" t="s">
-        <v>124</v>
+      <c r="F32" s="17" t="s">
+        <v>116</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="H32" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="A13:A19"/>
     <mergeCell ref="A20:A32"/>
     <mergeCell ref="B20:B29"/>
     <mergeCell ref="B1:B2"/>
@@ -2341,6 +2362,11 @@
     <mergeCell ref="E9:E10"/>
     <mergeCell ref="B3:B5"/>
     <mergeCell ref="B13:B16"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="A13:A19"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/internal_doc/05.测试设计/参数校验/元数据参数校验测试设计.xlsx
+++ b/internal_doc/05.测试设计/参数校验/元数据参数校验测试设计.xlsx
@@ -64,10 +64,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>options:Compressed</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>options:IsMainCL</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -157,16 +153,6 @@
     <t>1、取值非法，如test_123
 2、空串，如：dm.alter({AutoSplit:})  或  dm.alter({AutoSplit:''})
 3、options不指定任何参数，如：domain.alter()</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>listCollections
-语法：domain.listCollections()</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>listCollectionSpaces
-语法：omain.listCollectionSpaces()</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -229,12 +215,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">1、所属CS指定域，指定CL的Group为CS所属域中的group
-2、空串
-</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>AutoIndexId:true|false</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -355,11 +335,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>1、不存在的组
-2、空串，如：dm.alter({Groups:['']})  或 dm.alter({Groups:['']})</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>1、加条件查询，如：db.listCollections(“test”)
 2、空串，如：db.listCollections(“”)</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -520,11 +495,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>1、取值非法，如test
-2、空串</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Compressed:true|false</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -532,13 +502,6 @@
     <t>AutoSplit:true|false
 AutoSplit 必须配合散列分区和域使用，且不能与 Group 同时使用。
 如果在集合中没有指定AutoSplit，则使用所属域中的AutoSplit参数。</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、ShardingType:"range"，AutoSplit:true
-2、AutoSplit:和Group一起使用，如：AutoSplit:false,Group:group1
-3、取值非法，如test
-4、空串</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -1102,6 +1065,61 @@
       </rPr>
       <t>系统域  --get显示不出来</t>
     </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、不存在的组
+2、空串，如：dm.alter({Groups:['']})  或 dm.alter({Groups:})</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>listCollectionSpaces
+语法：domain.listCollectionSpaces()</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>listCollections
+语法：domain.listCollections()</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>name</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>options:Compressed</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>1、ShardingType:"range"，AutoSplit:true
+2、AutoSplit:和Group一起使用，如：AutoSplit:false,Group:group1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+3、取值非法，如test
+4、空串</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">1、所属CS指定域，指定CL的Group为CS所属域中不存在的group
+2、空串
+</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1293,7 +1311,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -1316,34 +1334,49 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1351,18 +1384,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1687,671 +1708,676 @@
   <dimension ref="A1:H32"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="6.375" style="11" customWidth="1"/>
-    <col min="2" max="2" width="18.5" style="12" customWidth="1"/>
-    <col min="3" max="3" width="11.25" style="12" customWidth="1"/>
-    <col min="4" max="4" width="27" style="12" customWidth="1"/>
-    <col min="5" max="5" width="4.75" style="13" customWidth="1"/>
-    <col min="6" max="6" width="28.375" style="12" customWidth="1"/>
-    <col min="7" max="7" width="30.375" style="12" customWidth="1"/>
-    <col min="8" max="8" width="9" style="12"/>
-    <col min="9" max="16384" width="9" style="11"/>
+    <col min="1" max="1" width="6.375" style="10" customWidth="1"/>
+    <col min="2" max="2" width="18.5" style="11" customWidth="1"/>
+    <col min="3" max="3" width="11.25" style="11" customWidth="1"/>
+    <col min="4" max="4" width="27" style="11" customWidth="1"/>
+    <col min="5" max="5" width="4.75" style="12" customWidth="1"/>
+    <col min="6" max="6" width="28.375" style="11" customWidth="1"/>
+    <col min="7" max="7" width="30.375" style="11" customWidth="1"/>
+    <col min="8" max="8" width="9" style="11"/>
+    <col min="9" max="16384" width="9" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="9" customFormat="1">
-      <c r="A1" s="18" t="s">
+    <row r="1" spans="1:8" s="8" customFormat="1">
+      <c r="A1" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" s="23" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="18" t="s">
+      <c r="C1" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="C1" s="18" t="s">
+      <c r="D1" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="D1" s="24" t="s">
+      <c r="E1" s="26"/>
+      <c r="F1" s="23" t="s">
         <v>19</v>
       </c>
-      <c r="E1" s="25"/>
-      <c r="F1" s="18" t="s">
+      <c r="G1" s="23" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="G1" s="18" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="18" t="s">
+    </row>
+    <row r="2" spans="1:8" s="8" customFormat="1" ht="25.5">
+      <c r="A2" s="24"/>
+      <c r="B2" s="24"/>
+      <c r="C2" s="24"/>
+      <c r="D2" s="2" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" s="9" customFormat="1" ht="25.5">
-      <c r="A2" s="19"/>
-      <c r="B2" s="19"/>
-      <c r="C2" s="19"/>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="F2" s="24"/>
+      <c r="G2" s="24"/>
+      <c r="H2" s="24"/>
+    </row>
+    <row r="3" spans="1:8" ht="76.5">
+      <c r="A3" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="F2" s="19"/>
-      <c r="G2" s="19"/>
-      <c r="H2" s="19"/>
-    </row>
-    <row r="3" spans="1:8" ht="76.5">
-      <c r="A3" s="26" t="s">
+      <c r="B3" s="29" t="s">
+        <v>110</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B3" s="28" t="s">
+      <c r="D3" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F3" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="G3" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="H3" s="9"/>
+    </row>
+    <row r="4" spans="1:8" ht="38.25">
+      <c r="A4" s="28"/>
+      <c r="B4" s="29"/>
+      <c r="C4" s="15" t="s">
+        <v>112</v>
+      </c>
+      <c r="D4" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F4" s="15" t="s">
+        <v>87</v>
+      </c>
+      <c r="G4" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="H4" s="9"/>
+    </row>
+    <row r="5" spans="1:8" ht="38.25">
+      <c r="A5" s="28"/>
+      <c r="B5" s="29"/>
+      <c r="C5" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="D5" s="15" t="s">
+        <v>88</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F5" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="H5" s="9"/>
+    </row>
+    <row r="6" spans="1:8" ht="63.75">
+      <c r="A6" s="28"/>
+      <c r="B6" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F6" s="16" t="s">
         <v>117</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="G6" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="H6" s="9"/>
+    </row>
+    <row r="7" spans="1:8" ht="38.25">
+      <c r="A7" s="28"/>
+      <c r="B7" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="E7" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D3" s="16" t="s">
+      <c r="F7" s="15" t="s">
         <v>118</v>
       </c>
-      <c r="E3" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="F3" s="16" t="s">
-        <v>93</v>
-      </c>
-      <c r="G3" s="16" t="s">
-        <v>123</v>
-      </c>
-      <c r="H3" s="10"/>
-    </row>
-    <row r="4" spans="1:8" ht="38.25">
-      <c r="A4" s="27"/>
-      <c r="B4" s="28"/>
-      <c r="C4" s="16" t="s">
-        <v>119</v>
-      </c>
-      <c r="D4" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="F4" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="G4" s="16" t="s">
+      <c r="G7" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="H4" s="10"/>
-    </row>
-    <row r="5" spans="1:8" ht="38.25">
-      <c r="A5" s="27"/>
-      <c r="B5" s="28"/>
-      <c r="C5" s="16" t="s">
-        <v>120</v>
-      </c>
-      <c r="D5" s="16" t="s">
-        <v>95</v>
-      </c>
-      <c r="E5" s="4" t="s">
+      <c r="H7" s="9"/>
+    </row>
+    <row r="8" spans="1:8" ht="38.25">
+      <c r="A8" s="28"/>
+      <c r="B8" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="F5" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="H5" s="10"/>
-    </row>
-    <row r="6" spans="1:8" ht="63.75">
-      <c r="A6" s="27"/>
-      <c r="B6" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="D6" s="16" t="s">
-        <v>59</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="F6" s="17" t="s">
-        <v>124</v>
-      </c>
-      <c r="G6" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="H6" s="10"/>
-    </row>
-    <row r="7" spans="1:8" ht="38.25">
-      <c r="A7" s="27"/>
-      <c r="B7" s="16" t="s">
-        <v>121</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D7" s="16" t="s">
-        <v>76</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="F7" s="16" t="s">
-        <v>125</v>
-      </c>
-      <c r="G7" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="H7" s="10"/>
-    </row>
-    <row r="8" spans="1:8" ht="38.25">
-      <c r="A8" s="27"/>
-      <c r="B8" s="1" t="s">
+      <c r="C8" s="5" t="s">
         <v>29</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>30</v>
       </c>
       <c r="D8" s="5"/>
       <c r="E8" s="4"/>
-      <c r="F8" s="17" t="s">
+      <c r="F8" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="H8" s="9"/>
+    </row>
+    <row r="9" spans="1:8" ht="51.75" customHeight="1">
+      <c r="A9" s="28"/>
+      <c r="B9" s="29" t="s">
         <v>31</v>
       </c>
-      <c r="G8" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="H8" s="10"/>
-    </row>
-    <row r="9" spans="1:8" ht="45.75" customHeight="1">
-      <c r="A9" s="27"/>
-      <c r="B9" s="28" t="s">
+      <c r="C9" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="D9" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="E9" s="30" t="s">
+        <v>1</v>
+      </c>
+      <c r="F9" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="G9" s="18" t="s">
+        <v>119</v>
+      </c>
+      <c r="H9" s="9"/>
+    </row>
+    <row r="10" spans="1:8" ht="76.5">
+      <c r="A10" s="28"/>
+      <c r="B10" s="29"/>
+      <c r="C10" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="D10" s="18" t="s">
+        <v>73</v>
+      </c>
+      <c r="E10" s="31"/>
+      <c r="F10" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="G10" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C9" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="D9" s="14" t="s">
-        <v>77</v>
-      </c>
-      <c r="E9" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="F9" s="17" t="s">
-        <v>97</v>
-      </c>
-      <c r="G9" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H9" s="10"/>
-    </row>
-    <row r="10" spans="1:8" ht="76.5">
-      <c r="A10" s="27"/>
-      <c r="B10" s="28"/>
-      <c r="C10" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="D10" s="14" t="s">
-        <v>78</v>
-      </c>
-      <c r="E10" s="30"/>
-      <c r="F10" s="15" t="s">
-        <v>98</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="H10" s="10"/>
+      <c r="H10" s="9"/>
     </row>
     <row r="11" spans="1:8" ht="51">
-      <c r="A11" s="27"/>
-      <c r="B11" s="1" t="s">
-        <v>34</v>
+      <c r="A11" s="28"/>
+      <c r="B11" s="18" t="s">
+        <v>121</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D11" s="7"/>
       <c r="E11" s="4"/>
-      <c r="F11" s="17" t="s">
-        <v>31</v>
+      <c r="F11" s="16" t="s">
+        <v>30</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="H11" s="10"/>
+        <v>60</v>
+      </c>
+      <c r="H11" s="9"/>
     </row>
     <row r="12" spans="1:8" ht="51">
-      <c r="A12" s="27"/>
-      <c r="B12" s="8" t="s">
-        <v>35</v>
+      <c r="A12" s="28"/>
+      <c r="B12" s="17" t="s">
+        <v>120</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D12" s="7"/>
       <c r="E12" s="4"/>
-      <c r="F12" s="17" t="s">
-        <v>31</v>
+      <c r="F12" s="16" t="s">
+        <v>30</v>
       </c>
       <c r="G12" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H12" s="9"/>
+    </row>
+    <row r="13" spans="1:8" ht="63.75">
+      <c r="A13" s="19" t="s">
+        <v>2</v>
+      </c>
+      <c r="B13" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="C13" s="18" t="s">
+        <v>122</v>
+      </c>
+      <c r="D13" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F13" s="14" t="s">
+        <v>92</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="H13" s="9"/>
+    </row>
+    <row r="14" spans="1:8" ht="89.25">
+      <c r="A14" s="19"/>
+      <c r="B14" s="21"/>
+      <c r="C14" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="D14" s="18" t="s">
+        <v>74</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F14" s="18" t="s">
+        <v>95</v>
+      </c>
+      <c r="G14" s="18" t="s">
+        <v>62</v>
+      </c>
+      <c r="H14" s="9"/>
+    </row>
+    <row r="15" spans="1:8" ht="38.25">
+      <c r="A15" s="19"/>
+      <c r="B15" s="21"/>
+      <c r="C15" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="D15" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F15" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="G15" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="H15" s="9"/>
+    </row>
+    <row r="16" spans="1:8" ht="51">
+      <c r="A16" s="19"/>
+      <c r="B16" s="22"/>
+      <c r="C16" s="18" t="s">
+        <v>85</v>
+      </c>
+      <c r="D16" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F16" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="G16" s="18" t="s">
+        <v>62</v>
+      </c>
+      <c r="H16" s="9"/>
+    </row>
+    <row r="17" spans="1:8" ht="51">
+      <c r="A17" s="19"/>
+      <c r="B17" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="H12" s="10"/>
-    </row>
-    <row r="13" spans="1:8" ht="63.75">
-      <c r="A13" s="20" t="s">
-        <v>2</v>
-      </c>
-      <c r="B13" s="21" t="s">
+      <c r="C17" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D17" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F17" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="G17" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="H17" s="9"/>
+    </row>
+    <row r="18" spans="1:8" ht="38.25">
+      <c r="A18" s="19"/>
+      <c r="B18" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="C18" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D18" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="E18" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D13" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E13" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="F13" s="15" t="s">
-        <v>99</v>
-      </c>
-      <c r="G13" s="1" t="s">
+      <c r="F18" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="G18" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="H13" s="10"/>
-    </row>
-    <row r="14" spans="1:8" ht="89.25">
-      <c r="A14" s="20"/>
-      <c r="B14" s="22"/>
-      <c r="C14" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="D14" s="14" t="s">
-        <v>79</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="F14" s="15" t="s">
-        <v>102</v>
-      </c>
-      <c r="G14" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="H14" s="10"/>
-    </row>
-    <row r="15" spans="1:8" ht="38.25">
-      <c r="A15" s="20"/>
-      <c r="B15" s="22"/>
-      <c r="C15" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D15" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="E15" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="F15" s="17" t="s">
-        <v>100</v>
-      </c>
-      <c r="G15" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="H15" s="10"/>
-    </row>
-    <row r="16" spans="1:8" ht="51">
-      <c r="A16" s="20"/>
-      <c r="B16" s="23"/>
-      <c r="C16" s="15" t="s">
-        <v>92</v>
-      </c>
-      <c r="D16" s="14" t="s">
-        <v>69</v>
-      </c>
-      <c r="E16" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="F16" s="15" t="s">
-        <v>101</v>
-      </c>
-      <c r="G16" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="H16" s="10"/>
-    </row>
-    <row r="17" spans="1:8" ht="51">
-      <c r="A17" s="20"/>
-      <c r="B17" s="1" t="s">
+      <c r="H18" s="9"/>
+    </row>
+    <row r="19" spans="1:8" ht="51">
+      <c r="A19" s="19"/>
+      <c r="B19" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="C17" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D17" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="E17" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="F17" s="17" t="s">
-        <v>103</v>
-      </c>
-      <c r="G17" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="H17" s="10"/>
-    </row>
-    <row r="18" spans="1:8" ht="38.25">
-      <c r="A18" s="20"/>
-      <c r="B18" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D18" s="14" t="s">
-        <v>80</v>
-      </c>
-      <c r="E18" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="F18" s="15" t="s">
-        <v>104</v>
-      </c>
-      <c r="G18" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="H18" s="10"/>
-    </row>
-    <row r="19" spans="1:8" ht="51">
-      <c r="A19" s="20"/>
-      <c r="B19" s="1" t="s">
-        <v>42</v>
-      </c>
       <c r="C19" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D19" s="5"/>
       <c r="E19" s="4"/>
-      <c r="F19" s="17" t="s">
-        <v>105</v>
+      <c r="F19" s="16" t="s">
+        <v>98</v>
       </c>
       <c r="G19" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H19" s="10"/>
+      <c r="H19" s="9"/>
     </row>
     <row r="20" spans="1:8" ht="63.75">
-      <c r="A20" s="20" t="s">
+      <c r="A20" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="B20" s="21" t="s">
-        <v>43</v>
+      <c r="B20" s="20" t="s">
+        <v>40</v>
       </c>
       <c r="C20" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D20" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="E20" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D20" s="14" t="s">
-        <v>81</v>
-      </c>
-      <c r="E20" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="F20" s="15" t="s">
+      <c r="F20" s="14" t="s">
+        <v>92</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="H20" s="9"/>
+    </row>
+    <row r="21" spans="1:8" ht="51">
+      <c r="A21" s="19"/>
+      <c r="B21" s="21"/>
+      <c r="C21" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="D21" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F21" s="18" t="s">
         <v>99</v>
       </c>
-      <c r="G20" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="H20" s="10"/>
-    </row>
-    <row r="21" spans="1:8" ht="51">
-      <c r="A21" s="20"/>
-      <c r="B21" s="22"/>
-      <c r="C21" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D21" s="14" t="s">
-        <v>83</v>
-      </c>
-      <c r="E21" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="F21" s="15" t="s">
-        <v>106</v>
-      </c>
-      <c r="G21" s="14" t="s">
-        <v>82</v>
-      </c>
-      <c r="H21" s="10"/>
+      <c r="G21" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="H21" s="9"/>
     </row>
     <row r="22" spans="1:8" ht="51.75">
-      <c r="A22" s="20"/>
-      <c r="B22" s="22"/>
+      <c r="A22" s="19"/>
+      <c r="B22" s="21"/>
       <c r="C22" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D22" s="14" t="s">
-        <v>44</v>
+      <c r="D22" s="13" t="s">
+        <v>41</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="F22" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="G22" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="H22" s="10"/>
+        <v>27</v>
+      </c>
+      <c r="F22" s="18" t="s">
+        <v>100</v>
+      </c>
+      <c r="G22" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="H22" s="9"/>
     </row>
     <row r="23" spans="1:8" ht="76.5">
-      <c r="A23" s="20"/>
-      <c r="B23" s="22"/>
+      <c r="A23" s="19"/>
+      <c r="B23" s="21"/>
       <c r="C23" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D23" s="14" t="s">
-        <v>73</v>
+      <c r="D23" s="13" t="s">
+        <v>68</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="F23" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="F23" s="18" t="s">
+        <v>101</v>
+      </c>
+      <c r="G23" s="18" t="s">
+        <v>69</v>
+      </c>
+      <c r="H23" s="9"/>
+    </row>
+    <row r="24" spans="1:8" ht="63.75">
+      <c r="A24" s="19"/>
+      <c r="B24" s="21"/>
+      <c r="C24" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="D24" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F24" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="G24" s="18" t="s">
+        <v>80</v>
+      </c>
+      <c r="H24" s="9"/>
+    </row>
+    <row r="25" spans="1:8" ht="27.75" customHeight="1">
+      <c r="A25" s="19"/>
+      <c r="B25" s="21"/>
+      <c r="C25" s="18" t="s">
+        <v>123</v>
+      </c>
+      <c r="D25" s="18" t="s">
+        <v>81</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F25" s="16" t="s">
+        <v>102</v>
+      </c>
+      <c r="G25" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="H25" s="9"/>
+    </row>
+    <row r="26" spans="1:8" ht="25.5">
+      <c r="A26" s="19"/>
+      <c r="B26" s="21"/>
+      <c r="C26" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="D26" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F26" s="16" t="s">
+        <v>103</v>
+      </c>
+      <c r="G26" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="H26" s="9"/>
+    </row>
+    <row r="27" spans="1:8" ht="89.25">
+      <c r="A27" s="19"/>
+      <c r="B27" s="21"/>
+      <c r="C27" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F27" s="16" t="s">
+        <v>104</v>
+      </c>
+      <c r="G27" s="18" t="s">
+        <v>124</v>
+      </c>
+      <c r="H27" s="9"/>
+    </row>
+    <row r="28" spans="1:8" ht="63.75">
+      <c r="A28" s="19"/>
+      <c r="B28" s="21"/>
+      <c r="C28" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="D28" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F28" s="18" t="s">
+        <v>105</v>
+      </c>
+      <c r="G28" s="18" t="s">
+        <v>125</v>
+      </c>
+      <c r="H28" s="9"/>
+    </row>
+    <row r="29" spans="1:8" ht="25.5">
+      <c r="A29" s="19"/>
+      <c r="B29" s="22"/>
+      <c r="C29" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F29" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H29" s="9"/>
+    </row>
+    <row r="30" spans="1:8" ht="76.5">
+      <c r="A30" s="19"/>
+      <c r="B30" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F30" s="14" t="s">
+        <v>107</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H30" s="9"/>
+    </row>
+    <row r="31" spans="1:8" ht="63.75">
+      <c r="A31" s="19"/>
+      <c r="B31" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F31" s="16" t="s">
         <v>108</v>
       </c>
-      <c r="G23" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="H23" s="10"/>
-    </row>
-    <row r="24" spans="1:8" ht="63.75">
-      <c r="A24" s="20"/>
-      <c r="B24" s="22"/>
-      <c r="C24" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D24" s="14" t="s">
-        <v>84</v>
-      </c>
-      <c r="E24" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="F24" s="17" t="s">
-        <v>90</v>
-      </c>
-      <c r="G24" s="14" t="s">
-        <v>85</v>
-      </c>
-      <c r="H24" s="10"/>
-    </row>
-    <row r="25" spans="1:8" ht="27.75" customHeight="1">
-      <c r="A25" s="20"/>
-      <c r="B25" s="22"/>
-      <c r="C25" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D25" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="E25" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="F25" s="17" t="s">
-        <v>109</v>
-      </c>
-      <c r="G25" s="14" t="s">
-        <v>86</v>
-      </c>
-      <c r="H25" s="10"/>
-    </row>
-    <row r="26" spans="1:8" ht="25.5">
-      <c r="A26" s="20"/>
-      <c r="B26" s="22"/>
-      <c r="C26" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D26" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="E26" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="F26" s="17" t="s">
-        <v>110</v>
-      </c>
-      <c r="G26" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="H26" s="10"/>
-    </row>
-    <row r="27" spans="1:8" ht="89.25">
-      <c r="A27" s="20"/>
-      <c r="B27" s="22"/>
-      <c r="C27" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D27" s="14" t="s">
-        <v>88</v>
-      </c>
-      <c r="E27" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="F27" s="17" t="s">
-        <v>111</v>
-      </c>
-      <c r="G27" s="14" t="s">
-        <v>89</v>
-      </c>
-      <c r="H27" s="10"/>
-    </row>
-    <row r="28" spans="1:8" ht="63.75">
-      <c r="A28" s="20"/>
-      <c r="B28" s="22"/>
-      <c r="C28" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D28" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="E28" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="F28" s="15" t="s">
-        <v>112</v>
-      </c>
-      <c r="G28" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="H28" s="10"/>
-    </row>
-    <row r="29" spans="1:8" ht="25.5">
-      <c r="A29" s="20"/>
-      <c r="B29" s="23"/>
-      <c r="C29" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D29" s="1" t="s">
+      <c r="G31" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E29" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="F29" s="15" t="s">
-        <v>113</v>
-      </c>
-      <c r="G29" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="H29" s="10"/>
-    </row>
-    <row r="30" spans="1:8" ht="76.5">
-      <c r="A30" s="20"/>
-      <c r="B30" s="1" t="s">
+      <c r="H31" s="9"/>
+    </row>
+    <row r="32" spans="1:8" ht="51">
+      <c r="A32" s="19"/>
+      <c r="B32" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C30" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="E30" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="F30" s="15" t="s">
-        <v>114</v>
-      </c>
-      <c r="G30" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="H30" s="10"/>
-    </row>
-    <row r="31" spans="1:8" ht="63.75">
-      <c r="A31" s="20"/>
-      <c r="B31" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="E31" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="F31" s="17" t="s">
-        <v>115</v>
-      </c>
-      <c r="G31" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="H31" s="10"/>
-    </row>
-    <row r="32" spans="1:8" ht="51">
-      <c r="A32" s="20"/>
-      <c r="B32" s="1" t="s">
-        <v>53</v>
-      </c>
       <c r="C32" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D32" s="5"/>
       <c r="E32" s="4"/>
-      <c r="F32" s="17" t="s">
-        <v>116</v>
+      <c r="F32" s="16" t="s">
+        <v>109</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="H32" s="10"/>
+        <v>50</v>
+      </c>
+      <c r="H32" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="A13:A19"/>
     <mergeCell ref="A20:A32"/>
     <mergeCell ref="B20:B29"/>
     <mergeCell ref="B1:B2"/>
@@ -2362,11 +2388,6 @@
     <mergeCell ref="E9:E10"/>
     <mergeCell ref="B3:B5"/>
     <mergeCell ref="B13:B16"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="A13:A19"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
